--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">6</t>
+      <t xml:space="preserve">7</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/2/2026</t>
+      <t xml:space="preserve">2/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/8/2026</t>
+      <t xml:space="preserve">2/15/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -901,8 +901,8 @@
       <c r="E15" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F15" s="14">
-        <v>1</v>
+      <c r="F15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G15" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-75</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D16" s="14">
         <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="I16" s="14">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="J16" s="14">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="K16" s="15">
-        <v>-53.846153846153</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="L16" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-81.818181818181</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="N16" s="15">
-        <v>-95.081967213114</v>
+        <v>-92.857142857142</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-16.666666666666</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I17" s="14">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.846153846153</v>
+        <v>-9.375</v>
       </c>
       <c r="L17" s="15">
-        <v>92.307692307692</v>
+        <v>52.631578947368</v>
       </c>
       <c r="M17" s="15">
-        <v>127.272727272727</v>
+        <v>141.666666666667</v>
       </c>
       <c r="N17" s="15">
-        <v>-47.916666666666</v>
+        <v>-44.230769230769</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1028,28 +1028,28 @@
         <v>4</v>
       </c>
       <c r="G18" s="14">
+        <v>1</v>
+      </c>
+      <c r="H18" s="15">
+        <v>300</v>
+      </c>
+      <c r="I18" s="14">
         <v>5</v>
-      </c>
-      <c r="H18" s="15">
-        <v>-20</v>
-      </c>
-      <c r="I18" s="14">
-        <v>4</v>
       </c>
       <c r="J18" s="14">
         <v>7</v>
       </c>
       <c r="K18" s="15">
-        <v>-42.857142857142</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="L18" s="15">
-        <v>-63.636363636363</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="M18" s="15">
-        <v>-66.666666666666</v>
+        <v>-58.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.666666666666</v>
+        <v>-94.117647058823</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-14.285714285714</v>
+        <v>40</v>
       </c>
       <c r="F19" s="14">
         <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-18.181818181818</v>
+        <v>-25</v>
       </c>
       <c r="I19" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="J19" s="14">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="K19" s="15">
-        <v>-10.344827586206</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L19" s="15">
-        <v>30</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-18.75</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.019607843137</v>
+        <v>-43.859649122807</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,7 +1098,7 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D20" s="13" t="s">
         <v>20</v>
@@ -1107,31 +1107,31 @@
         <v>21</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>166.666666666667</v>
       </c>
       <c r="I20" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="J20" s="14">
         <v>9</v>
       </c>
       <c r="K20" s="15">
-        <v>-22.222222222222</v>
+        <v>22.222222222222</v>
       </c>
       <c r="L20" s="15">
-        <v>-65</v>
+        <v>-54.166666666666</v>
       </c>
       <c r="M20" s="15">
-        <v>-12.5</v>
+        <v>10</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.463414634146</v>
+        <v>-89</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="D21" s="17">
         <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>-13.333333333333</v>
+        <v>26.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="G21" s="17">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>-18.965517241379</v>
+        <v>-5.263157894736</v>
       </c>
       <c r="I21" s="17">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="J21" s="17">
-        <v>88</v>
+        <v>103</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.590909090909</v>
+        <v>-14.563106796116</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.479452054794</v>
+        <v>-6.382978723404</v>
       </c>
       <c r="M21" s="18">
-        <v>-28.125</v>
+        <v>-18.518518518518</v>
       </c>
       <c r="N21" s="18">
-        <v>-82.03125</v>
+        <v>-80.090497737556</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>2</v>
       </c>
-      <c r="D22" s="14">
-        <v>2</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>150</v>
       </c>
       <c r="M22" s="15">
-        <v>-50</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D23" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-33.333333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G23" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-18.181818181818</v>
+        <v>-31.25</v>
       </c>
       <c r="I23" s="14">
-        <v>11</v>
+        <v>16</v>
       </c>
       <c r="J23" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="K23" s="15">
-        <v>-35.294117647058</v>
+        <v>-30.434782608695</v>
       </c>
       <c r="L23" s="15">
-        <v>175</v>
+        <v>220</v>
       </c>
       <c r="M23" s="15">
-        <v>-8.333333333333</v>
+        <v>14.285714285714</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>6</v>
+        <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E24" s="15">
-        <v>-14.285714285714</v>
+        <v>-20</v>
       </c>
       <c r="F24" s="14">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H24" s="15">
-        <v>-15.384615384615</v>
+        <v>-12.195121951219</v>
       </c>
       <c r="I24" s="14">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="J24" s="14">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.090909090909</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L24" s="15">
-        <v>-3.846153846153</v>
+        <v>-6.060606060606</v>
       </c>
       <c r="M24" s="15">
-        <v>-47.368421052631</v>
+        <v>-43.636363636363</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1305,32 +1305,32 @@
       <c r="C25" s="14">
         <v>2</v>
       </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="D25" s="14">
+        <v>6</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-66.666666666666</v>
       </c>
       <c r="F25" s="14">
         <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>44.444444444444</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J25" s="14">
-        <v>16</v>
+        <v>22</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>-18.181818181818</v>
       </c>
       <c r="L25" s="15">
-        <v>-5.882352941176</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="E26" s="15">
-        <v>75</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F26" s="14">
         <v>22</v>
       </c>
       <c r="G26" s="14">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H26" s="15">
-        <v>10</v>
+        <v>-12</v>
       </c>
       <c r="I26" s="14">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="J26" s="14">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="K26" s="15">
-        <v>12</v>
+        <v>-17.948717948717</v>
       </c>
       <c r="L26" s="15">
         <v>-20</v>
       </c>
       <c r="M26" s="15">
-        <v>21.739130434782</v>
+        <v>28</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1393,8 +1393,8 @@
       <c r="E27" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F27" s="14">
-        <v>1</v>
+      <c r="F27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G27" s="13" t="s">
         <v>20</v>
@@ -1425,32 +1425,32 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D28" s="14">
+      <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-75</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>-80</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">7</t>
+      <t xml:space="preserve">8</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/9/2026</t>
+      <t xml:space="preserve">2/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/15/2026</t>
+      <t xml:space="preserve">2/22/2026</t>
     </r>
   </si>
   <si>
@@ -692,10 +692,10 @@
     <col min="2" max="2" width="12.495057" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="6.168446" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="6.168446" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.433768" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="6.168446" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="9.964413" bestFit="1" customWidth="1"/>
@@ -854,26 +854,26 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="13" t="s">
-        <v>21</v>
+      <c r="D14" s="14">
+        <v>1</v>
+      </c>
+      <c r="E14" s="15">
+        <v>-100</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>21</v>
+      <c r="G14" s="14">
+        <v>1</v>
+      </c>
+      <c r="H14" s="15">
+        <v>-100</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J14" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K14" s="15">
         <v>-100</v>
@@ -934,81 +934,81 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-40</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I16" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="J16" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="K16" s="15">
-        <v>-41.176470588235</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="L16" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="M16" s="15">
-        <v>-71.428571428571</v>
+        <v>-67.567567567567</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.857142857142</v>
+        <v>-92.638036809816</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="14">
+      <c r="C17" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D17" s="14">
         <v>4</v>
       </c>
-      <c r="D17" s="14">
-        <v>6</v>
-      </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F17" s="14">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>-5.263157894736</v>
+        <v>-31.25</v>
       </c>
       <c r="I17" s="14">
         <v>29</v>
       </c>
       <c r="J17" s="14">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="K17" s="15">
-        <v>-9.375</v>
+        <v>-19.444444444444</v>
       </c>
       <c r="L17" s="15">
-        <v>52.631578947368</v>
+        <v>20.833333333333</v>
       </c>
       <c r="M17" s="15">
-        <v>141.666666666667</v>
+        <v>107.142857142857</v>
       </c>
       <c r="N17" s="15">
-        <v>-44.230769230769</v>
+        <v>-50.847457627118</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D18" s="14">
+        <v>2</v>
+      </c>
+      <c r="E18" s="15">
+        <v>50</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H18" s="15">
-        <v>300</v>
+        <v>150</v>
       </c>
       <c r="I18" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="K18" s="15">
-        <v>-28.571428571428</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>-58.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="M18" s="15">
-        <v>-58.333333333333</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N18" s="15">
-        <v>-94.117647058823</v>
+        <v>-91.752577319587</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E19" s="15">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H19" s="15">
-        <v>-25</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I19" s="14">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="J19" s="14">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="K19" s="15">
-        <v>-5.882352941176</v>
+        <v>0</v>
       </c>
       <c r="L19" s="15">
-        <v>33.333333333333</v>
+        <v>40.740740740740</v>
       </c>
       <c r="M19" s="15">
-        <v>-17.948717948717</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.859649122807</v>
+        <v>-40.625</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>1</v>
+      </c>
+      <c r="D20" s="14">
+        <v>1</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H20" s="15">
-        <v>166.666666666667</v>
+        <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="J20" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="K20" s="15">
-        <v>22.222222222222</v>
+        <v>20</v>
       </c>
       <c r="L20" s="15">
-        <v>-54.166666666666</v>
+        <v>-52</v>
       </c>
       <c r="M20" s="15">
-        <v>10</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="N20" s="15">
-        <v>-89</v>
+        <v>-90.082644628099</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>26.666666666666</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F21" s="17">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
         <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>-5.263157894736</v>
+        <v>-10.526315789473</v>
       </c>
       <c r="I21" s="17">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="J21" s="17">
-        <v>103</v>
+        <v>117</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.563106796116</v>
+        <v>-14.529914529914</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.382978723404</v>
+        <v>-8.256880733944</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.518518518518</v>
+        <v>-18.699186991869</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.090497737556</v>
+        <v>-80.46875</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1180,7 +1180,7 @@
         <v>29</v>
       </c>
       <c r="C22" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G22" s="14">
         <v>2</v>
       </c>
       <c r="H22" s="15">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="I22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J22" s="14">
         <v>2</v>
       </c>
       <c r="K22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="M22" s="15">
-        <v>-16.666666666666</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>1</v>
+      </c>
+      <c r="D23" s="14">
         <v>5</v>
       </c>
-      <c r="D23" s="14">
-        <v>6</v>
-      </c>
       <c r="E23" s="15">
-        <v>-16.666666666666</v>
+        <v>-80</v>
       </c>
       <c r="F23" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H23" s="15">
-        <v>-31.25</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="I23" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="J23" s="14">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="K23" s="15">
-        <v>-30.434782608695</v>
+        <v>-39.285714285714</v>
       </c>
       <c r="L23" s="15">
-        <v>220</v>
+        <v>88.888888888888</v>
       </c>
       <c r="M23" s="15">
-        <v>14.285714285714</v>
+        <v>6.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1265,34 +1265,34 @@
         <v>12</v>
       </c>
       <c r="D24" s="14">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="E24" s="15">
-        <v>-20</v>
+        <v>140</v>
       </c>
       <c r="F24" s="14">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="G24" s="14">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="H24" s="15">
-        <v>-12.195121951219</v>
+        <v>0</v>
       </c>
       <c r="I24" s="14">
-        <v>62</v>
+        <v>74</v>
       </c>
       <c r="J24" s="14">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.428571428571</v>
+        <v>-1.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.060606060606</v>
+        <v>-8.641975308641</v>
       </c>
       <c r="M24" s="15">
-        <v>-43.636363636363</v>
+        <v>-36.206896551724</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>2</v>
-      </c>
-      <c r="D25" s="14">
-        <v>6</v>
-      </c>
-      <c r="E25" s="15">
-        <v>-66.666666666666</v>
+        <v>4</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I25" s="14">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="J25" s="14">
         <v>22</v>
       </c>
       <c r="K25" s="15">
-        <v>-18.181818181818</v>
+        <v>0</v>
       </c>
       <c r="L25" s="15">
-        <v>-14.285714285714</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
+        <v>12</v>
+      </c>
+      <c r="D26" s="14">
         <v>4</v>
       </c>
-      <c r="D26" s="14">
-        <v>14</v>
-      </c>
       <c r="E26" s="15">
-        <v>-71.428571428571</v>
+        <v>200</v>
       </c>
       <c r="F26" s="14">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="G26" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H26" s="15">
-        <v>-12</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I26" s="14">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="K26" s="15">
-        <v>-17.948717948717</v>
+        <v>2.325581395348</v>
       </c>
       <c r="L26" s="15">
-        <v>-20</v>
+        <v>0</v>
       </c>
       <c r="M26" s="15">
-        <v>28</v>
+        <v>51.724137931034</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="14">
         <v>2</v>
-      </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F28" s="14">
-        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J28" s="14">
         <v>5</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
-      </c>
-      <c r="L28" s="13" t="s">
-        <v>21</v>
+        <v>-60</v>
+      </c>
+      <c r="L28" s="15">
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,26 +1469,26 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>-100</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K29" s="15">
         <v>-100</v>
@@ -1510,26 +1510,26 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>-100</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
       </c>
       <c r="J30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K30" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">8</t>
+      <t xml:space="preserve">9</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/16/2026</t>
+      <t xml:space="preserve">2/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/22/2026</t>
+      <t xml:space="preserve">3/1/2026</t>
     </r>
   </si>
   <si>
@@ -854,11 +854,11 @@
       <c r="C14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="14">
-        <v>1</v>
-      </c>
-      <c r="E14" s="15">
-        <v>-100</v>
+      <c r="D14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F14" s="13" t="s">
         <v>20</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-80</v>
+        <v>-83.333333333333</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,122 +934,122 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E16" s="15">
         <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
         <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-36.363636363636</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="I16" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="K16" s="15">
-        <v>-36.842105263157</v>
+        <v>-35</v>
       </c>
       <c r="L16" s="15">
-        <v>-33.333333333333</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="M16" s="15">
-        <v>-67.567567567567</v>
+        <v>-65.789473684210</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.638036809816</v>
+        <v>-92.934782608695</v>
       </c>
     </row>
     <row r="17" spans="1:14">
       <c r="A17" s="13" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="13" t="s">
-        <v>20</v>
+      <c r="C17" s="14">
+        <v>9</v>
       </c>
       <c r="D17" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-100</v>
+        <v>350</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="G17" s="14">
         <v>16</v>
       </c>
       <c r="H17" s="15">
-        <v>-31.25</v>
+        <v>6.25</v>
       </c>
       <c r="I17" s="14">
-        <v>29</v>
+        <v>39</v>
       </c>
       <c r="J17" s="14">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="K17" s="15">
-        <v>-19.444444444444</v>
+        <v>2.631578947368</v>
       </c>
       <c r="L17" s="15">
-        <v>20.833333333333</v>
+        <v>56</v>
       </c>
       <c r="M17" s="15">
-        <v>107.142857142857</v>
+        <v>178.571428571429</v>
       </c>
       <c r="N17" s="15">
-        <v>-50.847457627118</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>50</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>150</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
         <v>8</v>
       </c>
       <c r="J18" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.111111111111</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-33.333333333333</v>
+        <v>-50</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.752577319587</v>
+        <v>-92.727272727272</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>0</v>
+        <v>-40</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="H19" s="15">
-        <v>-13.043478260869</v>
+        <v>-9.523809523809</v>
       </c>
       <c r="I19" s="14">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="J19" s="14">
-        <v>38</v>
+        <v>43</v>
       </c>
       <c r="K19" s="15">
-        <v>0</v>
+        <v>-4.651162790697</v>
       </c>
       <c r="L19" s="15">
-        <v>40.740740740740</v>
+        <v>20.588235294117</v>
       </c>
       <c r="M19" s="15">
-        <v>-19.148936170212</v>
+        <v>-29.310344827586</v>
       </c>
       <c r="N19" s="15">
-        <v>-40.625</v>
+        <v>-42.253521126760</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,10 +1101,10 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
@@ -1116,22 +1116,22 @@
         <v>100</v>
       </c>
       <c r="I20" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J20" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K20" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-52</v>
+        <v>-55.172413793103</v>
       </c>
       <c r="M20" s="15">
-        <v>-7.692307692307</v>
+        <v>-7.142857142857</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.082644628099</v>
+        <v>-90.579710144927</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="E21" s="18">
-        <v>-28.571428571428</v>
+        <v>7.692307692307</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
         <v>57</v>
       </c>
       <c r="H21" s="18">
-        <v>-10.526315789473</v>
+        <v>0</v>
       </c>
       <c r="I21" s="17">
-        <v>100</v>
+        <v>115</v>
       </c>
       <c r="J21" s="17">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="K21" s="18">
-        <v>-14.529914529914</v>
+        <v>-11.538461538461</v>
       </c>
       <c r="L21" s="18">
-        <v>-8.256880733944</v>
+        <v>-5.737704918032</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.699186991869</v>
+        <v>-17.857142857142</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.46875</v>
+        <v>-80.069324090121</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1207,7 +1207,7 @@
         <v>200</v>
       </c>
       <c r="L22" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
         <v>-14.285714285714</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E23" s="15">
-        <v>-80</v>
+        <v>50</v>
       </c>
       <c r="F23" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H23" s="15">
-        <v>-47.058823529411</v>
+        <v>-25</v>
       </c>
       <c r="I23" s="14">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="J23" s="14">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="K23" s="15">
-        <v>-39.285714285714</v>
+        <v>-30</v>
       </c>
       <c r="L23" s="15">
-        <v>88.888888888888</v>
+        <v>110</v>
       </c>
       <c r="M23" s="15">
-        <v>6.25</v>
+        <v>31.25</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>5</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>140</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="G24" s="14">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="H24" s="15">
-        <v>0</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I24" s="14">
-        <v>74</v>
+        <v>84</v>
       </c>
       <c r="J24" s="14">
-        <v>75</v>
+        <v>93</v>
       </c>
       <c r="K24" s="15">
-        <v>-1.333333333333</v>
+        <v>-9.677419354838</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.641975308641</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="M24" s="15">
-        <v>-36.206896551724</v>
+        <v>-38.235294117647</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>4</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="14">
+        <v>10</v>
+      </c>
+      <c r="E25" s="15">
+        <v>-100</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
         <v>22</v>
       </c>
       <c r="J25" s="14">
-        <v>22</v>
+        <v>32</v>
       </c>
       <c r="K25" s="15">
-        <v>0</v>
+        <v>-31.25</v>
       </c>
       <c r="L25" s="15">
-        <v>-24.137931034482</v>
+        <v>-26.666666666666</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>12</v>
+        <v>1</v>
       </c>
       <c r="D26" s="14">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>200</v>
+        <v>-87.5</v>
       </c>
       <c r="F26" s="14">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="G26" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>16.666666666666</v>
+        <v>-23.333333333333</v>
       </c>
       <c r="I26" s="14">
         <v>44</v>
       </c>
       <c r="J26" s="14">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="K26" s="15">
-        <v>2.325581395348</v>
+        <v>-13.725490196078</v>
       </c>
       <c r="L26" s="15">
-        <v>0</v>
+        <v>-15.384615384615</v>
       </c>
       <c r="M26" s="15">
-        <v>51.724137931034</v>
+        <v>29.411764705882</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>1</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-33.333333333333</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>2</v>
       </c>
       <c r="J28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="13" t="s">
         <v>20</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="13" t="s">
         <v>20</v>
@@ -1616,8 +1616,8 @@
       <c r="E33" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F33" s="14">
-        <v>1</v>
+      <c r="F33" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G33" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">9</t>
+      <t xml:space="preserve">10</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">2/23/2026</t>
+      <t xml:space="preserve">3/2/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/1/2026</t>
+      <t xml:space="preserve">3/8/2026</t>
     </r>
   </si>
   <si>
@@ -881,8 +881,8 @@
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="M14" s="13" t="s">
-        <v>21</v>
+      <c r="M14" s="15">
+        <v>-100</v>
       </c>
       <c r="N14" s="15">
         <v>-100</v>
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
         <v>1</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
+        <v>7</v>
+      </c>
+      <c r="G16" s="14">
         <v>8</v>
       </c>
-      <c r="G16" s="14">
-        <v>11</v>
-      </c>
       <c r="H16" s="15">
-        <v>-27.272727272727</v>
+        <v>-12.5</v>
       </c>
       <c r="I16" s="14">
         <v>13</v>
       </c>
       <c r="J16" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="K16" s="15">
-        <v>-35</v>
+        <v>-38.095238095238</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.777777777777</v>
+        <v>-31.578947368421</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.789473684210</v>
+        <v>-68.292682926829</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.934782608695</v>
+        <v>-93.719806763285</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E17" s="15">
-        <v>350</v>
+        <v>-37.5</v>
       </c>
       <c r="F17" s="14">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="H17" s="15">
-        <v>6.25</v>
+        <v>-5</v>
       </c>
       <c r="I17" s="14">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="J17" s="14">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="K17" s="15">
-        <v>2.631578947368</v>
+        <v>-4.347826086956</v>
       </c>
       <c r="L17" s="15">
-        <v>56</v>
+        <v>57.142857142857</v>
       </c>
       <c r="M17" s="15">
-        <v>178.571428571429</v>
+        <v>175</v>
       </c>
       <c r="N17" s="15">
-        <v>-40</v>
+        <v>-43.589743589743</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
         <v>5</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="J18" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="K18" s="15">
-        <v>-27.272727272727</v>
+        <v>-25</v>
       </c>
       <c r="L18" s="15">
-        <v>-50</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.727272727272</v>
+        <v>-92.561983471074</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
+        <v>-22.222222222222</v>
+      </c>
+      <c r="F19" s="14">
+        <v>21</v>
+      </c>
+      <c r="G19" s="14">
+        <v>23</v>
+      </c>
+      <c r="H19" s="15">
+        <v>-8.695652173913</v>
+      </c>
+      <c r="I19" s="14">
+        <v>48</v>
+      </c>
+      <c r="J19" s="14">
+        <v>52</v>
+      </c>
+      <c r="K19" s="15">
+        <v>-7.692307692307</v>
+      </c>
+      <c r="L19" s="15">
+        <v>29.729729729729</v>
+      </c>
+      <c r="M19" s="15">
+        <v>-29.411764705882</v>
+      </c>
+      <c r="N19" s="15">
         <v>-40</v>
-      </c>
-      <c r="F19" s="14">
-        <v>19</v>
-      </c>
-      <c r="G19" s="14">
-        <v>21</v>
-      </c>
-      <c r="H19" s="15">
-        <v>-9.523809523809</v>
-      </c>
-      <c r="I19" s="14">
-        <v>41</v>
-      </c>
-      <c r="J19" s="14">
-        <v>43</v>
-      </c>
-      <c r="K19" s="15">
-        <v>-4.651162790697</v>
-      </c>
-      <c r="L19" s="15">
-        <v>20.588235294117</v>
-      </c>
-      <c r="M19" s="15">
-        <v>-29.310344827586</v>
-      </c>
-      <c r="N19" s="15">
-        <v>-42.253521126760</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>2</v>
+      </c>
+      <c r="D20" s="14">
         <v>1</v>
       </c>
-      <c r="D20" s="14">
-        <v>3</v>
-      </c>
       <c r="E20" s="15">
-        <v>-66.666666666666</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="I20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="J20" s="14">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-55.172413793103</v>
+        <v>-51.724137931034</v>
       </c>
       <c r="M20" s="15">
-        <v>-7.142857142857</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.579710144927</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>7.692307692307</v>
+        <v>-25</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" s="17">
-        <v>57</v>
+        <v>62</v>
       </c>
       <c r="H21" s="18">
-        <v>0</v>
+        <v>-6.451612903225</v>
       </c>
       <c r="I21" s="17">
-        <v>115</v>
+        <v>129</v>
       </c>
       <c r="J21" s="17">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="K21" s="18">
-        <v>-11.538461538461</v>
+        <v>-14</v>
       </c>
       <c r="L21" s="18">
-        <v>-5.737704918032</v>
+        <v>-3.731343283582</v>
       </c>
       <c r="M21" s="18">
-        <v>-17.857142857142</v>
+        <v>-18.867924528301</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.069324090121</v>
+        <v>-80.123266563944</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,13 +1189,13 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>5</v>
-      </c>
-      <c r="G22" s="14">
-        <v>2</v>
-      </c>
-      <c r="H22" s="15">
-        <v>150</v>
+        <v>3</v>
+      </c>
+      <c r="G22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-14.285714285714</v>
+        <v>-25</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D23" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
         <v>12</v>
       </c>
       <c r="G23" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-25</v>
+        <v>-36.842105263157</v>
       </c>
       <c r="I23" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="J23" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="K23" s="15">
-        <v>-30</v>
+        <v>-36.111111111111</v>
       </c>
       <c r="L23" s="15">
-        <v>110</v>
+        <v>109.090909090909</v>
       </c>
       <c r="M23" s="15">
-        <v>31.25</v>
+        <v>21.052631578947</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="E24" s="15">
-        <v>-44.444444444444</v>
+        <v>-25</v>
       </c>
       <c r="F24" s="14">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="H24" s="15">
-        <v>-11.111111111111</v>
+        <v>-14</v>
       </c>
       <c r="I24" s="14">
-        <v>84</v>
+        <v>93</v>
       </c>
       <c r="J24" s="14">
-        <v>93</v>
+        <v>105</v>
       </c>
       <c r="K24" s="15">
-        <v>-9.677419354838</v>
+        <v>-11.428571428571</v>
       </c>
       <c r="L24" s="15">
-        <v>-6.666666666666</v>
+        <v>-7</v>
       </c>
       <c r="M24" s="15">
-        <v>-38.235294117647</v>
+        <v>-39.215686274509</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
+      <c r="C25" s="14">
+        <v>4</v>
       </c>
       <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>33.333333333333</v>
+      </c>
+      <c r="F25" s="14">
         <v>10</v>
       </c>
-      <c r="E25" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F25" s="14">
-        <v>8</v>
-      </c>
       <c r="G25" s="14">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>-47.368421052631</v>
       </c>
       <c r="I25" s="14">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="J25" s="14">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="K25" s="15">
-        <v>-31.25</v>
+        <v>-25.714285714285</v>
       </c>
       <c r="L25" s="15">
-        <v>-26.666666666666</v>
+        <v>-18.75</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-87.5</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H26" s="15">
-        <v>-23.333333333333</v>
+        <v>-24.242424242424</v>
       </c>
       <c r="I26" s="14">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="J26" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K26" s="15">
-        <v>-13.725490196078</v>
+        <v>-10.344827586206</v>
       </c>
       <c r="L26" s="15">
-        <v>-15.384615384615</v>
+        <v>-8.771929824561</v>
       </c>
       <c r="M26" s="15">
-        <v>29.411764705882</v>
+        <v>26.829268292682</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>2</v>
       </c>
       <c r="D28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I28" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J28" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-66.666666666666</v>
+        <v>-50</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">10</t>
+      <t xml:space="preserve">11</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/2/2026</t>
+      <t xml:space="preserve">3/9/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/8/2026</t>
+      <t xml:space="preserve">3/15/2026</t>
     </r>
   </si>
   <si>
@@ -895,29 +895,29 @@
       <c r="C15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>-100</v>
       </c>
       <c r="F15" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>-100</v>
       </c>
       <c r="I15" s="14">
         <v>1</v>
       </c>
       <c r="J15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -926,48 +926,48 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-83.333333333333</v>
+        <v>-87.5</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>2</v>
       </c>
       <c r="D16" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F16" s="14">
+        <v>5</v>
+      </c>
+      <c r="G16" s="14">
         <v>7</v>
       </c>
-      <c r="G16" s="14">
-        <v>8</v>
-      </c>
       <c r="H16" s="15">
-        <v>-12.5</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I16" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="J16" s="14">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-38.095238095238</v>
+        <v>-37.5</v>
       </c>
       <c r="L16" s="15">
-        <v>-31.578947368421</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.292682926829</v>
+        <v>-65.116279069767</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.719806763285</v>
+        <v>-93.392070484581</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>5</v>
       </c>
-      <c r="D17" s="14">
-        <v>8</v>
-      </c>
       <c r="E17" s="15">
-        <v>-37.5</v>
+        <v>-20</v>
       </c>
       <c r="F17" s="14">
         <v>19</v>
       </c>
       <c r="G17" s="14">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J17" s="14">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="K17" s="15">
-        <v>-4.347826086956</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L17" s="15">
-        <v>57.142857142857</v>
+        <v>54.838709677419</v>
       </c>
       <c r="M17" s="15">
-        <v>175</v>
+        <v>140</v>
       </c>
       <c r="N17" s="15">
-        <v>-43.589743589743</v>
+        <v>-40</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G18" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I18" s="14">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K18" s="15">
-        <v>-25</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="L18" s="15">
-        <v>-57.142857142857</v>
+        <v>-52</v>
       </c>
       <c r="M18" s="15">
-        <v>-52.631578947368</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.561983471074</v>
+        <v>-90.697674418604</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="E19" s="15">
-        <v>-22.222222222222</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G19" s="14">
-        <v>23</v>
+        <v>32</v>
       </c>
       <c r="H19" s="15">
-        <v>-8.695652173913</v>
+        <v>-43.75</v>
       </c>
       <c r="I19" s="14">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="J19" s="14">
-        <v>52</v>
+        <v>66</v>
       </c>
       <c r="K19" s="15">
-        <v>-7.692307692307</v>
+        <v>-21.212121212121</v>
       </c>
       <c r="L19" s="15">
-        <v>29.729729729729</v>
+        <v>30</v>
       </c>
       <c r="M19" s="15">
-        <v>-29.411764705882</v>
+        <v>-30.666666666666</v>
       </c>
       <c r="N19" s="15">
-        <v>-40</v>
+        <v>-42.222222222222</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="14">
-        <v>5</v>
-      </c>
       <c r="H20" s="15">
-        <v>20</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J20" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="K20" s="15">
         <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-51.724137931034</v>
+        <v>-51.612903225806</v>
       </c>
       <c r="M20" s="15">
         <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.909090909090</v>
+        <v>-91.428571428571</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1142,45 +1142,45 @@
         <v>15</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="E21" s="18">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="F21" s="17">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="G21" s="17">
-        <v>62</v>
+        <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-6.451612903225</v>
+        <v>-26.388888888888</v>
       </c>
       <c r="I21" s="17">
-        <v>129</v>
+        <v>143</v>
       </c>
       <c r="J21" s="17">
-        <v>150</v>
+        <v>175</v>
       </c>
       <c r="K21" s="18">
-        <v>-14</v>
+        <v>-18.285714285714</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.731343283582</v>
+        <v>-3.378378378378</v>
       </c>
       <c r="M21" s="18">
-        <v>-18.867924528301</v>
+        <v>-19.209039548022</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.123266563944</v>
+        <v>-79.915730337078</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1189,7 +1189,7 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>20</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>6</v>
       </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F23" s="14">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
         <v>19</v>
       </c>
       <c r="H23" s="15">
-        <v>-36.842105263157</v>
+        <v>-57.894736842105</v>
       </c>
       <c r="I23" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="J23" s="14">
-        <v>36</v>
+        <v>42</v>
       </c>
       <c r="K23" s="15">
-        <v>-36.111111111111</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="L23" s="15">
-        <v>109.090909090909</v>
+        <v>71.428571428571</v>
       </c>
       <c r="M23" s="15">
-        <v>21.052631578947</v>
+        <v>9.090909090909</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="15">
-        <v>-25</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="F24" s="14">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G24" s="14">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="H24" s="15">
-        <v>-14</v>
+        <v>-13.043478260869</v>
       </c>
       <c r="I24" s="14">
-        <v>93</v>
+        <v>102</v>
       </c>
       <c r="J24" s="14">
-        <v>105</v>
+        <v>116</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.428571428571</v>
+        <v>-12.068965517241</v>
       </c>
       <c r="L24" s="15">
-        <v>-7</v>
+        <v>-9.734513274336</v>
       </c>
       <c r="M24" s="15">
-        <v>-39.215686274509</v>
+        <v>-40.697674418604</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,23 +1302,23 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="14">
-        <v>4</v>
-      </c>
-      <c r="D25" s="14">
-        <v>3</v>
-      </c>
-      <c r="E25" s="15">
-        <v>33.333333333333</v>
+      <c r="C25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D25" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E25" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="H25" s="15">
-        <v>-47.368421052631</v>
+        <v>-38.461538461538</v>
       </c>
       <c r="I25" s="14">
         <v>26</v>
@@ -1330,7 +1330,7 @@
         <v>-25.714285714285</v>
       </c>
       <c r="L25" s="15">
-        <v>-18.75</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="E26" s="15">
-        <v>14.285714285714</v>
+        <v>-10</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H26" s="15">
-        <v>-24.242424242424</v>
+        <v>3.448275862068</v>
       </c>
       <c r="I26" s="14">
-        <v>52</v>
+        <v>61</v>
       </c>
       <c r="J26" s="14">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.344827586206</v>
+        <v>-10.294117647058</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.771929824561</v>
+        <v>-12.857142857142</v>
       </c>
       <c r="M26" s="15">
-        <v>26.829268292682</v>
+        <v>27.083333333333</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1387,29 +1387,29 @@
       <c r="C27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>-100</v>
       </c>
       <c r="F27" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>-100</v>
       </c>
       <c r="I27" s="14">
         <v>1</v>
       </c>
       <c r="J27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>21</v>
@@ -1428,32 +1428,32 @@
       <c r="C28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>8</v>
       </c>
       <c r="K28" s="15">
-        <v>-50</v>
+        <v>-25</v>
       </c>
       <c r="L28" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1551,29 +1551,29 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H31" s="13" t="s">
-        <v>21</v>
+      <c r="G31" s="14">
+        <v>1</v>
+      </c>
+      <c r="H31" s="15">
+        <v>-100</v>
       </c>
       <c r="I31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="J31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="K31" s="13" t="s">
-        <v>21</v>
+      <c r="J31" s="14">
+        <v>1</v>
+      </c>
+      <c r="K31" s="15">
+        <v>-100</v>
       </c>
       <c r="L31" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">11</t>
+      <t xml:space="preserve">12</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/9/2026</t>
+      <t xml:space="preserve">3/16/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/15/2026</t>
+      <t xml:space="preserve">3/22/2026</t>
     </r>
   </si>
   <si>
@@ -863,11 +863,11 @@
       <c r="F14" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G14" s="14">
-        <v>1</v>
-      </c>
-      <c r="H14" s="15">
-        <v>-100</v>
+      <c r="G14" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I14" s="13" t="s">
         <v>20</v>
@@ -892,32 +892,32 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F15" s="13" t="s">
-        <v>20</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
+        <v>2</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="L15" s="13" t="s">
         <v>21</v>
@@ -926,7 +926,7 @@
         <v>21</v>
       </c>
       <c r="N15" s="15">
-        <v>-87.5</v>
+        <v>-66.666666666666</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>3</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-33.333333333333</v>
+        <v>1</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
+        <v>4</v>
+      </c>
+      <c r="G16" s="14">
         <v>5</v>
       </c>
-      <c r="G16" s="14">
-        <v>7</v>
-      </c>
       <c r="H16" s="15">
-        <v>-28.571428571428</v>
+        <v>-20</v>
       </c>
       <c r="I16" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J16" s="14">
         <v>24</v>
       </c>
       <c r="K16" s="15">
-        <v>-37.5</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="L16" s="15">
-        <v>-28.571428571428</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.116279069767</v>
+        <v>-64.444444444444</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.392070484581</v>
+        <v>-93.650793650793</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D17" s="14">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="E17" s="15">
-        <v>-20</v>
+        <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>23.529411764705</v>
       </c>
       <c r="I17" s="14">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="J17" s="14">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="K17" s="15">
-        <v>-5.882352941176</v>
+        <v>-3.773584905660</v>
       </c>
       <c r="L17" s="15">
-        <v>54.838709677419</v>
+        <v>45.714285714285</v>
       </c>
       <c r="M17" s="15">
-        <v>140</v>
+        <v>112.5</v>
       </c>
       <c r="N17" s="15">
-        <v>-40</v>
+        <v>-42.045454545454</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>3</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="E18" s="15">
-        <v>200</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>6</v>
       </c>
       <c r="H18" s="15">
-        <v>16.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
         <v>12</v>
       </c>
       <c r="J18" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>-7.692307692307</v>
+        <v>-20</v>
       </c>
       <c r="L18" s="15">
+        <v>-53.846153846153</v>
+      </c>
+      <c r="M18" s="15">
         <v>-52</v>
       </c>
-      <c r="M18" s="15">
-        <v>-45.454545454545</v>
-      </c>
       <c r="N18" s="15">
-        <v>-90.697674418604</v>
+        <v>-91.666666666666</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-64.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="G19" s="14">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.75</v>
+        <v>-45.945945945945</v>
       </c>
       <c r="I19" s="14">
-        <v>52</v>
+        <v>57</v>
       </c>
       <c r="J19" s="14">
-        <v>66</v>
+        <v>75</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.212121212121</v>
+        <v>-24</v>
       </c>
       <c r="L19" s="15">
-        <v>30</v>
+        <v>23.913043478260</v>
       </c>
       <c r="M19" s="15">
-        <v>-30.666666666666</v>
+        <v>-31.325301204819</v>
       </c>
       <c r="N19" s="15">
-        <v>-42.222222222222</v>
+        <v>-43.564356435643</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="F20" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
         <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>0</v>
       </c>
       <c r="I20" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="J20" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="L20" s="15">
-        <v>-51.612903225806</v>
+        <v>-47.058823529411</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>5.882352941176</v>
       </c>
       <c r="N20" s="15">
-        <v>-91.428571428571</v>
+        <v>-90.425531914893</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,48 +1139,48 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="E21" s="18">
-        <v>-40</v>
+        <v>0</v>
       </c>
       <c r="F21" s="17">
-        <v>53</v>
+        <v>57</v>
       </c>
       <c r="G21" s="17">
         <v>72</v>
       </c>
       <c r="H21" s="18">
-        <v>-26.388888888888</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="I21" s="17">
-        <v>143</v>
+        <v>157</v>
       </c>
       <c r="J21" s="17">
-        <v>175</v>
+        <v>189</v>
       </c>
       <c r="K21" s="18">
-        <v>-18.285714285714</v>
+        <v>-16.931216931216</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.378378378378</v>
+        <v>-3.680981595092</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.209039548022</v>
+        <v>-19.897959183673</v>
       </c>
       <c r="N21" s="18">
-        <v>-79.915730337078</v>
+        <v>-80</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="14">
-        <v>1</v>
+      <c r="C22" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D22" s="13" t="s">
         <v>20</v>
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-25</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
+      <c r="E23" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F23" s="14">
         <v>6</v>
       </c>
-      <c r="E23" s="15">
-        <v>-83.333333333333</v>
-      </c>
-      <c r="F23" s="14">
-        <v>8</v>
-      </c>
       <c r="G23" s="14">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="H23" s="15">
-        <v>-57.894736842105</v>
+        <v>-60</v>
       </c>
       <c r="I23" s="14">
         <v>24</v>
       </c>
       <c r="J23" s="14">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="K23" s="15">
-        <v>-42.857142857142</v>
+        <v>-44.186046511627</v>
       </c>
       <c r="L23" s="15">
-        <v>71.428571428571</v>
+        <v>33.333333333333</v>
       </c>
       <c r="M23" s="15">
         <v>9.090909090909</v>
@@ -1265,34 +1265,34 @@
         <v>10</v>
       </c>
       <c r="D24" s="14">
-        <v>11</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>-9.090909090909</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="F24" s="14">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G24" s="14">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="H24" s="15">
-        <v>-13.043478260869</v>
+        <v>-34.482758620689</v>
       </c>
       <c r="I24" s="14">
-        <v>102</v>
+        <v>112</v>
       </c>
       <c r="J24" s="14">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="K24" s="15">
-        <v>-12.068965517241</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.734513274336</v>
+        <v>-8.943089430894</v>
       </c>
       <c r="M24" s="15">
-        <v>-40.697674418604</v>
+        <v>-41.361256544502</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1302,35 +1302,35 @@
       <c r="A25" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="C25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D25" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E25" s="13" t="s">
-        <v>21</v>
+      <c r="C25" s="14">
+        <v>4</v>
+      </c>
+      <c r="D25" s="14">
+        <v>3</v>
+      </c>
+      <c r="E25" s="15">
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
         <v>8</v>
       </c>
       <c r="G25" s="14">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H25" s="15">
-        <v>-38.461538461538</v>
+        <v>-50</v>
       </c>
       <c r="I25" s="14">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="J25" s="14">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="K25" s="15">
-        <v>-25.714285714285</v>
+        <v>-21.052631578947</v>
       </c>
       <c r="L25" s="15">
-        <v>-23.529411764705</v>
+        <v>-25</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="E26" s="15">
-        <v>-10</v>
+        <v>66.666666666666</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="G26" s="14">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>3.448275862068</v>
+        <v>-10.714285714285</v>
       </c>
       <c r="I26" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="J26" s="14">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="K26" s="15">
-        <v>-10.294117647058</v>
+        <v>-5.633802816901</v>
       </c>
       <c r="L26" s="15">
-        <v>-12.857142857142</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="M26" s="15">
-        <v>27.083333333333</v>
+        <v>21.818181818181</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,32 +1384,32 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F27" s="13" t="s">
-        <v>20</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
+        <v>2</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-75</v>
+        <v>-25</v>
       </c>
       <c r="L27" s="13" t="s">
         <v>21</v>
@@ -1425,35 +1425,35 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
+      <c r="C28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D28" s="14">
         <v>2</v>
       </c>
-      <c r="D28" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>33.333333333333</v>
+        <v>-20</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="K28" s="15">
-        <v>-25</v>
+        <v>-40</v>
       </c>
       <c r="L28" s="15">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1478,11 +1478,11 @@
       <c r="F29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G29" s="14">
-        <v>1</v>
-      </c>
-      <c r="H29" s="15">
-        <v>-100</v>
+      <c r="G29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I29" s="13" t="s">
         <v>20</v>
@@ -1519,11 +1519,11 @@
       <c r="F30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="G30" s="14">
-        <v>1</v>
-      </c>
-      <c r="H30" s="15">
-        <v>-100</v>
+      <c r="G30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I30" s="13" t="s">
         <v>20</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">12</t>
+      <t xml:space="preserve">13</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/16/2026</t>
+      <t xml:space="preserve">3/23/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/22/2026</t>
+      <t xml:space="preserve">3/29/2026</t>
     </r>
   </si>
   <si>
@@ -892,8 +892,8 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
-        <v>2</v>
+      <c r="C15" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D15" s="13" t="s">
         <v>20</v>
@@ -919,11 +919,11 @@
       <c r="K15" s="15">
         <v>-25</v>
       </c>
-      <c r="L15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="M15" s="13" t="s">
-        <v>21</v>
+      <c r="L15" s="15">
+        <v>200</v>
+      </c>
+      <c r="M15" s="15">
+        <v>200</v>
       </c>
       <c r="N15" s="15">
         <v>-66.666666666666</v>
@@ -934,40 +934,40 @@
         <v>23</v>
       </c>
       <c r="C16" s="14">
-        <v>1</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+        <v>2</v>
+      </c>
+      <c r="D16" s="14">
+        <v>2</v>
+      </c>
+      <c r="E16" s="15">
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H16" s="15">
-        <v>-20</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I16" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J16" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="K16" s="15">
-        <v>-33.333333333333</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="L16" s="15">
-        <v>-27.272727272727</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="M16" s="15">
-        <v>-64.444444444444</v>
+        <v>-65.384615384615</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.650793650793</v>
+        <v>-93.283582089552</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -984,31 +984,31 @@
         <v>50</v>
       </c>
       <c r="F17" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G17" s="14">
         <v>17</v>
       </c>
       <c r="H17" s="15">
-        <v>23.529411764705</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="I17" s="14">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="J17" s="14">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.773584905660</v>
+        <v>-1.818181818181</v>
       </c>
       <c r="L17" s="15">
-        <v>45.714285714285</v>
+        <v>22.727272727272</v>
       </c>
       <c r="M17" s="15">
-        <v>112.5</v>
+        <v>125</v>
       </c>
       <c r="N17" s="15">
-        <v>-42.045454545454</v>
+        <v>-49.532710280373</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1018,38 +1018,38 @@
       <c r="C18" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D18" s="14">
-        <v>2</v>
-      </c>
-      <c r="E18" s="15">
-        <v>-100</v>
+      <c r="D18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E18" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F18" s="14">
+        <v>5</v>
+      </c>
+      <c r="G18" s="14">
         <v>4</v>
       </c>
-      <c r="G18" s="14">
-        <v>6</v>
-      </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>25</v>
       </c>
       <c r="I18" s="14">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="J18" s="14">
         <v>15</v>
       </c>
       <c r="K18" s="15">
-        <v>-20</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="L18" s="15">
-        <v>-53.846153846153</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="M18" s="15">
-        <v>-52</v>
+        <v>-48.148148148148</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.666666666666</v>
+        <v>-91.25</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F19" s="14">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="G19" s="14">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="H19" s="15">
-        <v>-45.945945945945</v>
+        <v>-40</v>
       </c>
       <c r="I19" s="14">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="J19" s="14">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="K19" s="15">
-        <v>-24</v>
+        <v>-21.794871794871</v>
       </c>
       <c r="L19" s="15">
-        <v>23.913043478260</v>
+        <v>27.083333333333</v>
       </c>
       <c r="M19" s="15">
-        <v>-31.325301204819</v>
+        <v>-35.789473684210</v>
       </c>
       <c r="N19" s="15">
-        <v>-43.564356435643</v>
+        <v>-46.017699115044</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
+        <v>1</v>
+      </c>
+      <c r="D20" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E20" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F20" s="14">
+        <v>7</v>
+      </c>
+      <c r="G20" s="14">
         <v>3</v>
       </c>
-      <c r="D20" s="14">
-        <v>1</v>
-      </c>
-      <c r="E20" s="15">
-        <v>200</v>
-      </c>
-      <c r="F20" s="14">
-        <v>6</v>
-      </c>
-      <c r="G20" s="14">
-        <v>6</v>
-      </c>
       <c r="H20" s="15">
-        <v>0</v>
+        <v>133.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" s="14">
         <v>16</v>
       </c>
       <c r="K20" s="15">
-        <v>12.5</v>
+        <v>18.75</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.058823529411</v>
+        <v>-48.648648648648</v>
       </c>
       <c r="M20" s="15">
-        <v>5.882352941176</v>
+        <v>5.555555555555</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.425531914893</v>
+        <v>-90.547263681592</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="E21" s="18">
-        <v>0</v>
+        <v>42.857142857142</v>
       </c>
       <c r="F21" s="17">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="H21" s="18">
-        <v>-20.833333333333</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>157</v>
+        <v>169</v>
       </c>
       <c r="J21" s="17">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.931216931216</v>
+        <v>-13.775510204081</v>
       </c>
       <c r="L21" s="18">
-        <v>-3.680981595092</v>
+        <v>-6.111111111111</v>
       </c>
       <c r="M21" s="18">
-        <v>-19.897959183673</v>
+        <v>-22.831050228310</v>
       </c>
       <c r="N21" s="18">
-        <v>-80</v>
+        <v>-80.462427745664</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-45.454545454545</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>2</v>
       </c>
       <c r="D23" s="14">
         <v>1</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F23" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G23" s="14">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H23" s="15">
-        <v>-60</v>
+        <v>-64.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="J23" s="14">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>-44.186046511627</v>
+        <v>-40.909090909090</v>
       </c>
       <c r="L23" s="15">
-        <v>33.333333333333</v>
+        <v>18.181818181818</v>
       </c>
       <c r="M23" s="15">
-        <v>9.090909090909</v>
+        <v>13.043478260869</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="E24" s="15">
-        <v>-41.176470588235</v>
+        <v>-30.769230769230</v>
       </c>
       <c r="F24" s="14">
         <v>38</v>
       </c>
       <c r="G24" s="14">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="H24" s="15">
-        <v>-34.482758620689</v>
+        <v>-28.301886792452</v>
       </c>
       <c r="I24" s="14">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="J24" s="14">
-        <v>133</v>
+        <v>146</v>
       </c>
       <c r="K24" s="15">
-        <v>-15.789473684210</v>
+        <v>-17.808219178082</v>
       </c>
       <c r="L24" s="15">
-        <v>-8.943089430894</v>
+        <v>-9.774436090225</v>
       </c>
       <c r="M24" s="15">
-        <v>-41.361256544502</v>
+        <v>-41.176470588235</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>50</v>
       </c>
       <c r="F25" s="14">
+        <v>11</v>
+      </c>
+      <c r="G25" s="14">
         <v>8</v>
       </c>
-      <c r="G25" s="14">
-        <v>16</v>
-      </c>
       <c r="H25" s="15">
-        <v>-50</v>
+        <v>37.5</v>
       </c>
       <c r="I25" s="14">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="J25" s="14">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="K25" s="15">
-        <v>-21.052631578947</v>
+        <v>-17.5</v>
       </c>
       <c r="L25" s="15">
-        <v>-25</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="D26" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>66.666666666666</v>
+        <v>12.5</v>
       </c>
       <c r="F26" s="14">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
         <v>28</v>
       </c>
       <c r="H26" s="15">
-        <v>-10.714285714285</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I26" s="14">
-        <v>67</v>
+        <v>76</v>
       </c>
       <c r="J26" s="14">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="K26" s="15">
-        <v>-5.633802816901</v>
+        <v>-3.797468354430</v>
       </c>
       <c r="L26" s="15">
-        <v>-11.842105263157</v>
+        <v>-14.606741573033</v>
       </c>
       <c r="M26" s="15">
-        <v>21.818181818181</v>
+        <v>11.764705882352</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1385,7 +1385,7 @@
         <v>34</v>
       </c>
       <c r="C27" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1394,25 +1394,25 @@
         <v>21</v>
       </c>
       <c r="F27" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>-25</v>
-      </c>
-      <c r="L27" s="13" t="s">
-        <v>21</v>
+        <v>0</v>
+      </c>
+      <c r="L27" s="15">
+        <v>300</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,7 +1429,7 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
@@ -1438,22 +1438,22 @@
         <v>4</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-20</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="K28" s="15">
-        <v>-40</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="L28" s="15">
-        <v>0</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">13</t>
+      <t xml:space="preserve">14</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/23/2026</t>
+      <t xml:space="preserve">3/30/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/29/2026</t>
+      <t xml:space="preserve">4/5/2026</t>
     </r>
   </si>
   <si>
@@ -902,54 +902,54 @@
         <v>21</v>
       </c>
       <c r="F15" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="I15" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="J15" s="14">
         <v>4</v>
       </c>
       <c r="K15" s="15">
-        <v>-25</v>
+        <v>0</v>
       </c>
       <c r="L15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>2</v>
-      </c>
-      <c r="D16" s="14">
-        <v>2</v>
-      </c>
-      <c r="E16" s="15">
-        <v>0</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
         <v>5</v>
       </c>
       <c r="G16" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H16" s="15">
-        <v>-16.666666666666</v>
+        <v>0</v>
       </c>
       <c r="I16" s="14">
         <v>18</v>
@@ -961,13 +961,13 @@
         <v>-30.769230769230</v>
       </c>
       <c r="L16" s="15">
-        <v>-21.739130434782</v>
+        <v>-25</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.384615384615</v>
+        <v>-68.421052631578</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.283582089552</v>
+        <v>-93.75</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>2</v>
+      </c>
+      <c r="D17" s="14">
         <v>3</v>
       </c>
-      <c r="D17" s="14">
-        <v>2</v>
-      </c>
       <c r="E17" s="15">
-        <v>50</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="H17" s="15">
-        <v>-11.764705882352</v>
+        <v>0</v>
       </c>
       <c r="I17" s="14">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="J17" s="14">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.818181818181</v>
+        <v>-3.448275862068</v>
       </c>
       <c r="L17" s="15">
-        <v>22.727272727272</v>
+        <v>27.272727272727</v>
       </c>
       <c r="M17" s="15">
-        <v>125</v>
+        <v>107.407407407407</v>
       </c>
       <c r="N17" s="15">
-        <v>-49.532710280373</v>
+        <v>-52.542372881355</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D18" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="13" t="s">
-        <v>21</v>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="14">
+        <v>1</v>
+      </c>
+      <c r="E18" s="15">
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="I18" s="14">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="K18" s="15">
-        <v>-6.666666666666</v>
+        <v>-6.25</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.148148148148</v>
+        <v>-46.428571428571</v>
       </c>
       <c r="M18" s="15">
-        <v>-48.148148148148</v>
+        <v>-53.125</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.25</v>
+        <v>-91.620111731843</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D19" s="14">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>33.333333333333</v>
+        <v>-75</v>
       </c>
       <c r="F19" s="14">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G19" s="14">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="H19" s="15">
-        <v>-40</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="I19" s="14">
         <v>61</v>
       </c>
       <c r="J19" s="14">
-        <v>78</v>
+        <v>86</v>
       </c>
       <c r="K19" s="15">
-        <v>-21.794871794871</v>
+        <v>-29.069767441860</v>
       </c>
       <c r="L19" s="15">
-        <v>27.083333333333</v>
+        <v>10.909090909090</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.789473684210</v>
+        <v>-37.755102040816</v>
       </c>
       <c r="N19" s="15">
-        <v>-46.017699115044</v>
+        <v>-51.968503937007</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>1</v>
-      </c>
-      <c r="D20" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E20" s="13" t="s">
-        <v>21</v>
+        <v>3</v>
+      </c>
+      <c r="D20" s="14">
+        <v>3</v>
+      </c>
+      <c r="E20" s="15">
+        <v>0</v>
       </c>
       <c r="F20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H20" s="15">
-        <v>133.333333333333</v>
+        <v>60</v>
       </c>
       <c r="I20" s="14">
+        <v>22</v>
+      </c>
+      <c r="J20" s="14">
         <v>19</v>
       </c>
-      <c r="J20" s="14">
-        <v>16</v>
-      </c>
       <c r="K20" s="15">
-        <v>18.75</v>
+        <v>15.789473684210</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.648648648648</v>
+        <v>-48.837209302325</v>
       </c>
       <c r="M20" s="15">
-        <v>5.555555555555</v>
+        <v>22.222222222222</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.547263681592</v>
+        <v>-89.671361502347</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="E21" s="18">
-        <v>42.857142857142</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="F21" s="17">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="G21" s="17">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="H21" s="18">
-        <v>-16.666666666666</v>
+        <v>-22.950819672131</v>
       </c>
       <c r="I21" s="17">
-        <v>169</v>
+        <v>176</v>
       </c>
       <c r="J21" s="17">
-        <v>196</v>
+        <v>211</v>
       </c>
       <c r="K21" s="18">
-        <v>-13.775510204081</v>
+        <v>-16.587677725118</v>
       </c>
       <c r="L21" s="18">
-        <v>-6.111111111111</v>
+        <v>-9.743589743589</v>
       </c>
       <c r="M21" s="18">
-        <v>-22.831050228310</v>
+        <v>-25.106382978723</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.462427745664</v>
+        <v>-81.336161187698</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1210,7 +1210,7 @@
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-53.846153846153</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>2</v>
-      </c>
-      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="E23" s="15">
-        <v>100</v>
+      <c r="D23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E23" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G23" s="14">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="H23" s="15">
-        <v>-64.285714285714</v>
+        <v>-50</v>
       </c>
       <c r="I23" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J23" s="14">
         <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>-40.909090909090</v>
+        <v>-38.636363636363</v>
       </c>
       <c r="L23" s="15">
-        <v>18.181818181818</v>
+        <v>12.5</v>
       </c>
       <c r="M23" s="15">
-        <v>13.043478260869</v>
+        <v>12.5</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="D24" s="14">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="E24" s="15">
-        <v>-30.769230769230</v>
+        <v>250</v>
       </c>
       <c r="F24" s="14">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="G24" s="14">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="H24" s="15">
-        <v>-28.301886792452</v>
+        <v>-6.666666666666</v>
       </c>
       <c r="I24" s="14">
-        <v>120</v>
+        <v>133</v>
       </c>
       <c r="J24" s="14">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.808219178082</v>
+        <v>-11.333333333333</v>
       </c>
       <c r="L24" s="15">
-        <v>-9.774436090225</v>
+        <v>-5.673758865248</v>
       </c>
       <c r="M24" s="15">
-        <v>-41.176470588235</v>
+        <v>-40.888888888888</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>50</v>
+        <v>400</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G25" s="14">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H25" s="15">
-        <v>37.5</v>
+        <v>100</v>
       </c>
       <c r="I25" s="14">
-        <v>33</v>
+        <v>38</v>
       </c>
       <c r="J25" s="14">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="K25" s="15">
-        <v>-17.5</v>
+        <v>-7.317073170731</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.428571428571</v>
+        <v>-19.148936170212</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="E26" s="15">
-        <v>12.5</v>
+        <v>-61.538461538461</v>
       </c>
       <c r="F26" s="14">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G26" s="14">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="H26" s="15">
-        <v>14.285714285714</v>
+        <v>-14.705882352941</v>
       </c>
       <c r="I26" s="14">
-        <v>76</v>
+        <v>81</v>
       </c>
       <c r="J26" s="14">
-        <v>79</v>
+        <v>92</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.797468354430</v>
+        <v>-11.956521739130</v>
       </c>
       <c r="L26" s="15">
-        <v>-14.606741573033</v>
+        <v>-10.989010989011</v>
       </c>
       <c r="M26" s="15">
-        <v>11.764705882352</v>
+        <v>10.958904109589</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,8 +1384,8 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
-        <v>1</v>
+      <c r="C27" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D27" s="13" t="s">
         <v>20</v>
@@ -1403,16 +1403,16 @@
         <v>200</v>
       </c>
       <c r="I27" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J27" s="14">
         <v>4</v>
       </c>
       <c r="K27" s="15">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="L27" s="15">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1429,31 +1429,31 @@
         <v>20</v>
       </c>
       <c r="D28" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E28" s="15">
         <v>-100</v>
       </c>
       <c r="F28" s="14">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-42.857142857142</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="J28" s="14">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-53.846153846153</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-14.285714285714</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">14</t>
+      <t xml:space="preserve">15</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">3/30/2026</t>
+      <t xml:space="preserve">4/6/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/5/2026</t>
+      <t xml:space="preserve">4/12/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="13" t="s">
-        <v>20</v>
+      <c r="C14" s="14">
+        <v>1</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="13" t="s">
-        <v>20</v>
+      <c r="F14" s="14">
+        <v>1</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -869,23 +869,23 @@
       <c r="H14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I14" s="13" t="s">
-        <v>20</v>
+      <c r="I14" s="14">
+        <v>1</v>
       </c>
       <c r="J14" s="14">
         <v>2</v>
       </c>
       <c r="K14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L14" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M14" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="N14" s="15">
-        <v>-100</v>
+        <v>-88.888888888888</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -904,11 +904,11 @@
       <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="14">
-        <v>1</v>
-      </c>
-      <c r="H15" s="15">
-        <v>200</v>
+      <c r="G15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I15" s="14">
         <v>4</v>
@@ -926,48 +926,48 @@
         <v>300</v>
       </c>
       <c r="N15" s="15">
-        <v>-60</v>
+        <v>-63.636363636363</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D16" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="13" t="s">
-        <v>21</v>
+      <c r="C16" s="14">
+        <v>1</v>
+      </c>
+      <c r="D16" s="14">
+        <v>6</v>
+      </c>
+      <c r="E16" s="15">
+        <v>-83.333333333333</v>
       </c>
       <c r="F16" s="14">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H16" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="I16" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="K16" s="15">
-        <v>-30.769230769230</v>
+        <v>-40.625</v>
       </c>
       <c r="L16" s="15">
-        <v>-25</v>
+        <v>-24</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.421052631578</v>
+        <v>-67.796610169491</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.75</v>
+        <v>-93.666666666666</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D17" s="14">
         <v>3</v>
       </c>
       <c r="E17" s="15">
-        <v>-33.333333333333</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F17" s="14">
         <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="H17" s="15">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="I17" s="14">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="J17" s="14">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="K17" s="15">
-        <v>-3.448275862068</v>
+        <v>-1.639344262295</v>
       </c>
       <c r="L17" s="15">
-        <v>27.272727272727</v>
+        <v>27.659574468085</v>
       </c>
       <c r="M17" s="15">
-        <v>107.407407407407</v>
+        <v>100</v>
       </c>
       <c r="N17" s="15">
-        <v>-52.542372881355</v>
+        <v>-51.612903225806</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
-        <v>1</v>
+      <c r="C18" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F18" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G18" s="14">
         <v>4</v>
       </c>
       <c r="H18" s="15">
-        <v>0</v>
+        <v>-75</v>
       </c>
       <c r="I18" s="14">
         <v>15</v>
       </c>
       <c r="J18" s="14">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="K18" s="15">
-        <v>-6.25</v>
+        <v>-11.764705882352</v>
       </c>
       <c r="L18" s="15">
-        <v>-46.428571428571</v>
+        <v>-48.275862068965</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.125</v>
+        <v>-55.882352941176</v>
       </c>
       <c r="N18" s="15">
-        <v>-91.620111731843</v>
+        <v>-92.227979274611</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="E19" s="15">
-        <v>-75</v>
+        <v>20</v>
       </c>
       <c r="F19" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G19" s="14">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="H19" s="15">
-        <v>-55.882352941176</v>
+        <v>-36</v>
       </c>
       <c r="I19" s="14">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="J19" s="14">
-        <v>86</v>
+        <v>91</v>
       </c>
       <c r="K19" s="15">
-        <v>-29.069767441860</v>
+        <v>-25.274725274725</v>
       </c>
       <c r="L19" s="15">
-        <v>10.909090909090</v>
+        <v>7.936507936507</v>
       </c>
       <c r="M19" s="15">
-        <v>-37.755102040816</v>
+        <v>-37.037037037037</v>
       </c>
       <c r="N19" s="15">
-        <v>-51.968503937007</v>
+        <v>-50.364963503649</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-50</v>
       </c>
       <c r="F20" s="14">
         <v>8</v>
       </c>
       <c r="G20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H20" s="15">
-        <v>60</v>
+        <v>33.333333333333</v>
       </c>
       <c r="I20" s="14">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="K20" s="15">
-        <v>15.789473684210</v>
+        <v>9.523809523809</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.837209302325</v>
+        <v>-47.727272727272</v>
       </c>
       <c r="M20" s="15">
-        <v>22.222222222222</v>
+        <v>15</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.671361502347</v>
+        <v>-89.545454545454</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D21" s="17">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E21" s="18">
-        <v>-46.666666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="F21" s="17">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G21" s="17">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="H21" s="18">
-        <v>-22.950819672131</v>
+        <v>-15.094339622641</v>
       </c>
       <c r="I21" s="17">
-        <v>176</v>
+        <v>190</v>
       </c>
       <c r="J21" s="17">
-        <v>211</v>
+        <v>228</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.587677725118</v>
+        <v>-16.666666666666</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.743589743589</v>
+        <v>-9.090909090909</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.106382978723</v>
+        <v>-25.196850393700</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.336161187698</v>
+        <v>-80.885311871227</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F22" s="14">
-        <v>1</v>
-      </c>
-      <c r="G22" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H22" s="13" t="s">
-        <v>21</v>
+      <c r="D22" s="14">
+        <v>3</v>
+      </c>
+      <c r="E22" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="G22" s="14">
+        <v>3</v>
+      </c>
+      <c r="H22" s="15">
+        <v>-100</v>
       </c>
       <c r="I22" s="14">
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="K22" s="15">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="L22" s="15">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="M22" s="15">
-        <v>-57.142857142857</v>
+        <v>-60</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,7 +1221,7 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D23" s="13" t="s">
         <v>20</v>
@@ -1230,28 +1230,28 @@
         <v>21</v>
       </c>
       <c r="F23" s="14">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H23" s="15">
-        <v>-50</v>
+        <v>200</v>
       </c>
       <c r="I23" s="14">
-        <v>27</v>
+        <v>30</v>
       </c>
       <c r="J23" s="14">
         <v>44</v>
       </c>
       <c r="K23" s="15">
-        <v>-38.636363636363</v>
+        <v>-31.818181818181</v>
       </c>
       <c r="L23" s="15">
-        <v>12.5</v>
+        <v>15.384615384615</v>
       </c>
       <c r="M23" s="15">
-        <v>12.5</v>
+        <v>7.142857142857</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="D24" s="14">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="E24" s="15">
-        <v>250</v>
+        <v>-58.823529411764</v>
       </c>
       <c r="F24" s="14">
-        <v>42</v>
+        <v>39</v>
       </c>
       <c r="G24" s="14">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="H24" s="15">
-        <v>-6.666666666666</v>
+        <v>-23.529411764705</v>
       </c>
       <c r="I24" s="14">
-        <v>133</v>
+        <v>140</v>
       </c>
       <c r="J24" s="14">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="K24" s="15">
-        <v>-11.333333333333</v>
+        <v>-16.167664670658</v>
       </c>
       <c r="L24" s="15">
-        <v>-5.673758865248</v>
+        <v>-7.284768211920</v>
       </c>
       <c r="M24" s="15">
-        <v>-40.888888888888</v>
+        <v>-41.422594142259</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
+        <v>1</v>
+      </c>
+      <c r="D25" s="14">
         <v>5</v>
       </c>
-      <c r="D25" s="14">
-        <v>1</v>
-      </c>
       <c r="E25" s="15">
-        <v>400</v>
+        <v>-80</v>
       </c>
       <c r="F25" s="14">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G25" s="14">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="H25" s="15">
-        <v>100</v>
+        <v>18.181818181818</v>
       </c>
       <c r="I25" s="14">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="J25" s="14">
-        <v>41</v>
+        <v>46</v>
       </c>
       <c r="K25" s="15">
-        <v>-7.317073170731</v>
+        <v>-15.217391304347</v>
       </c>
       <c r="L25" s="15">
-        <v>-19.148936170212</v>
+        <v>-22</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1347,34 +1347,34 @@
         <v>5</v>
       </c>
       <c r="D26" s="14">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="E26" s="15">
-        <v>-61.538461538461</v>
+        <v>150</v>
       </c>
       <c r="F26" s="14">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G26" s="14">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="H26" s="15">
-        <v>-14.705882352941</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I26" s="14">
-        <v>81</v>
+        <v>86</v>
       </c>
       <c r="J26" s="14">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="K26" s="15">
-        <v>-11.956521739130</v>
+        <v>-8.510638297872</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.989010989011</v>
+        <v>-13.131313131313</v>
       </c>
       <c r="M26" s="15">
-        <v>10.958904109589</v>
+        <v>10.256410256410</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1396,11 +1396,11 @@
       <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="14">
-        <v>1</v>
-      </c>
-      <c r="H27" s="15">
-        <v>200</v>
+      <c r="G27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="H27" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="I27" s="14">
         <v>5</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>2</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F28" s="14">
-        <v>2</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F28" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G28" s="14">
         <v>7</v>
       </c>
       <c r="H28" s="15">
-        <v>-71.428571428571</v>
+        <v>-100</v>
       </c>
       <c r="I28" s="14">
         <v>5</v>
@@ -1453,7 +1453,7 @@
         <v>-66.666666666666</v>
       </c>
       <c r="L28" s="15">
-        <v>-44.444444444444</v>
+        <v>-50</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,8 +1466,8 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="13" t="s">
-        <v>20</v>
+      <c r="C29" s="14">
+        <v>1</v>
       </c>
       <c r="D29" s="13" t="s">
         <v>20</v>
@@ -1475,8 +1475,8 @@
       <c r="E29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F29" s="13" t="s">
-        <v>20</v>
+      <c r="F29" s="14">
+        <v>1</v>
       </c>
       <c r="G29" s="13" t="s">
         <v>20</v>
@@ -1484,31 +1484,31 @@
       <c r="H29" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I29" s="13" t="s">
-        <v>20</v>
+      <c r="I29" s="14">
+        <v>1</v>
       </c>
       <c r="J29" s="14">
         <v>2</v>
       </c>
       <c r="K29" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M29" s="15">
-        <v>-100</v>
+        <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-100</v>
+        <v>-96.551724137931</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="13" t="s">
-        <v>20</v>
+      <c r="C30" s="14">
+        <v>1</v>
       </c>
       <c r="D30" s="13" t="s">
         <v>20</v>
@@ -1516,8 +1516,8 @@
       <c r="E30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F30" s="13" t="s">
-        <v>20</v>
+      <c r="F30" s="14">
+        <v>1</v>
       </c>
       <c r="G30" s="13" t="s">
         <v>20</v>
@@ -1525,23 +1525,23 @@
       <c r="H30" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="I30" s="13" t="s">
-        <v>20</v>
+      <c r="I30" s="14">
+        <v>1</v>
       </c>
       <c r="J30" s="14">
         <v>2</v>
       </c>
       <c r="K30" s="15">
-        <v>-100</v>
+        <v>-50</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
       </c>
       <c r="M30" s="15">
-        <v>-100</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-100</v>
+        <v>-95.833333333333</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>2</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">15</t>
+      <t xml:space="preserve">16</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/6/2026</t>
+      <t xml:space="preserve">4/13/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/12/2026</t>
+      <t xml:space="preserve">4/19/2026</t>
     </r>
   </si>
   <si>
@@ -851,8 +851,8 @@
       <c r="A14" s="13" t="s">
         <v>19</v>
       </c>
-      <c r="C14" s="14">
-        <v>1</v>
+      <c r="C14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D14" s="13" t="s">
         <v>20</v>
@@ -878,8 +878,8 @@
       <c r="K14" s="15">
         <v>-50</v>
       </c>
-      <c r="L14" s="13" t="s">
-        <v>21</v>
+      <c r="L14" s="15">
+        <v>0</v>
       </c>
       <c r="M14" s="15">
         <v>-50</v>
@@ -892,82 +892,82 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="13" t="s">
-        <v>21</v>
+      <c r="C15" s="14">
+        <v>2</v>
+      </c>
+      <c r="D15" s="14">
+        <v>1</v>
+      </c>
+      <c r="E15" s="15">
+        <v>100</v>
       </c>
       <c r="F15" s="14">
         <v>3</v>
       </c>
-      <c r="G15" s="13" t="s">
+      <c r="G15" s="14">
+        <v>1</v>
+      </c>
+      <c r="H15" s="15">
+        <v>200</v>
+      </c>
+      <c r="I15" s="14">
+        <v>6</v>
+      </c>
+      <c r="J15" s="14">
+        <v>5</v>
+      </c>
+      <c r="K15" s="15">
         <v>20</v>
       </c>
-      <c r="H15" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="I15" s="14">
-        <v>4</v>
-      </c>
-      <c r="J15" s="14">
-        <v>4</v>
-      </c>
-      <c r="K15" s="15">
-        <v>0</v>
-      </c>
       <c r="L15" s="15">
-        <v>300</v>
+        <v>500</v>
       </c>
       <c r="M15" s="15">
-        <v>300</v>
+        <v>200</v>
       </c>
       <c r="N15" s="15">
-        <v>-63.636363636363</v>
+        <v>-50</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>1</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D16" s="14">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E16" s="15">
-        <v>-83.333333333333</v>
+        <v>-100</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G16" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="H16" s="15">
-        <v>-50</v>
+        <v>-70</v>
       </c>
       <c r="I16" s="14">
         <v>19</v>
       </c>
       <c r="J16" s="14">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.625</v>
+        <v>-44.117647058823</v>
       </c>
       <c r="L16" s="15">
-        <v>-24</v>
+        <v>-29.629629629629</v>
       </c>
       <c r="M16" s="15">
-        <v>-67.796610169491</v>
+        <v>-68.333333333333</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.666666666666</v>
+        <v>-94.080996884735</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="D17" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="E17" s="15">
-        <v>33.333333333333</v>
+        <v>-83.333333333333</v>
       </c>
       <c r="F17" s="14">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G17" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H17" s="15">
-        <v>20</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I17" s="14">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="J17" s="14">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="K17" s="15">
-        <v>-1.639344262295</v>
+        <v>-8.955223880597</v>
       </c>
       <c r="L17" s="15">
-        <v>27.659574468085</v>
+        <v>24.489795918367</v>
       </c>
       <c r="M17" s="15">
-        <v>100</v>
+        <v>90.625</v>
       </c>
       <c r="N17" s="15">
-        <v>-51.612903225806</v>
+        <v>-54.135338345864</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
         <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G18" s="14">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H18" s="15">
-        <v>-75</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="J18" s="14">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.764705882352</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.275862068965</v>
+        <v>-50</v>
       </c>
       <c r="M18" s="15">
-        <v>-55.882352941176</v>
+        <v>-54.285714285714</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.227979274611</v>
+        <v>-92.488262910798</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E19" s="15">
-        <v>20</v>
+        <v>-50</v>
       </c>
       <c r="F19" s="14">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G19" s="14">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="H19" s="15">
-        <v>-36</v>
+        <v>-37.5</v>
       </c>
       <c r="I19" s="14">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="J19" s="14">
-        <v>91</v>
+        <v>99</v>
       </c>
       <c r="K19" s="15">
-        <v>-25.274725274725</v>
+        <v>-27.272727272727</v>
       </c>
       <c r="L19" s="15">
-        <v>7.936507936507</v>
+        <v>2.857142857142</v>
       </c>
       <c r="M19" s="15">
-        <v>-37.037037037037</v>
+        <v>-35.714285714285</v>
       </c>
       <c r="N19" s="15">
-        <v>-50.364963503649</v>
+        <v>-48.571428571428</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="14">
-        <v>1</v>
+      <c r="C20" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="D20" s="14">
         <v>2</v>
       </c>
       <c r="E20" s="15">
-        <v>-50</v>
+        <v>-100</v>
       </c>
       <c r="F20" s="14">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>33.333333333333</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="I20" s="14">
         <v>23</v>
       </c>
       <c r="J20" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K20" s="15">
-        <v>9.523809523809</v>
+        <v>0</v>
       </c>
       <c r="L20" s="15">
-        <v>-47.727272727272</v>
+        <v>-50</v>
       </c>
       <c r="M20" s="15">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.545454545454</v>
+        <v>-90.212765957446</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>13</v>
+        <v>8</v>
       </c>
       <c r="D21" s="17">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="E21" s="18">
-        <v>-23.529411764705</v>
+        <v>-60</v>
       </c>
       <c r="F21" s="17">
-        <v>45</v>
+        <v>39</v>
       </c>
       <c r="G21" s="17">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="H21" s="18">
-        <v>-15.094339622641</v>
+        <v>-33.898305084745</v>
       </c>
       <c r="I21" s="17">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="J21" s="17">
-        <v>228</v>
+        <v>248</v>
       </c>
       <c r="K21" s="18">
-        <v>-16.666666666666</v>
+        <v>-20.161290322580</v>
       </c>
       <c r="L21" s="18">
-        <v>-9.090909090909</v>
+        <v>-12.389380530973</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.196850393700</v>
+        <v>-25.563909774436</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.885311871227</v>
+        <v>-81.373471307619</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1183,7 +1183,7 @@
         <v>20</v>
       </c>
       <c r="D22" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E22" s="15">
         <v>-100</v>
@@ -1192,7 +1192,7 @@
         <v>20</v>
       </c>
       <c r="G22" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H22" s="15">
         <v>-100</v>
@@ -1201,10 +1201,10 @@
         <v>6</v>
       </c>
       <c r="J22" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="K22" s="15">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="L22" s="15">
         <v>50</v>
@@ -1220,35 +1220,35 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>3</v>
       </c>
-      <c r="D23" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>21</v>
+      <c r="E23" s="15">
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
         <v>6</v>
       </c>
       <c r="G23" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H23" s="15">
-        <v>200</v>
+        <v>50</v>
       </c>
       <c r="I23" s="14">
         <v>30</v>
       </c>
       <c r="J23" s="14">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.818181818181</v>
+        <v>-36.170212765957</v>
       </c>
       <c r="L23" s="15">
-        <v>15.384615384615</v>
+        <v>3.448275862068</v>
       </c>
       <c r="M23" s="15">
         <v>7.142857142857</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D24" s="14">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-58.823529411764</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F24" s="14">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G24" s="14">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="H24" s="15">
-        <v>-23.529411764705</v>
+        <v>-20.930232558139</v>
       </c>
       <c r="I24" s="14">
-        <v>140</v>
+        <v>145</v>
       </c>
       <c r="J24" s="14">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.167664670658</v>
+        <v>-17.613636363636</v>
       </c>
       <c r="L24" s="15">
-        <v>-7.284768211920</v>
+        <v>-11.585365853658</v>
       </c>
       <c r="M24" s="15">
-        <v>-41.422594142259</v>
+        <v>-44.015444015444</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>1</v>
       </c>
       <c r="D25" s="14">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>-80</v>
+        <v>0</v>
       </c>
       <c r="F25" s="14">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H25" s="15">
-        <v>18.181818181818</v>
+        <v>11.111111111111</v>
       </c>
       <c r="I25" s="14">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="J25" s="14">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="K25" s="15">
-        <v>-15.217391304347</v>
+        <v>-14.893617021276</v>
       </c>
       <c r="L25" s="15">
-        <v>-22</v>
+        <v>-20</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="D26" s="14">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="E26" s="15">
-        <v>150</v>
+        <v>37.5</v>
       </c>
       <c r="F26" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="G26" s="14">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="H26" s="15">
-        <v>-7.692307692307</v>
+        <v>-3.225806451612</v>
       </c>
       <c r="I26" s="14">
-        <v>86</v>
+        <v>97</v>
       </c>
       <c r="J26" s="14">
-        <v>94</v>
+        <v>102</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.510638297872</v>
+        <v>-4.901960784313</v>
       </c>
       <c r="L26" s="15">
-        <v>-13.131313131313</v>
+        <v>-10.185185185185</v>
       </c>
       <c r="M26" s="15">
-        <v>10.256410256410</v>
+        <v>16.867469879518</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,35 +1384,35 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="D27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="13" t="s">
-        <v>21</v>
+      <c r="C27" s="14">
+        <v>2</v>
+      </c>
+      <c r="D27" s="14">
+        <v>1</v>
+      </c>
+      <c r="E27" s="15">
+        <v>100</v>
       </c>
       <c r="F27" s="14">
         <v>3</v>
       </c>
-      <c r="G27" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H27" s="13" t="s">
-        <v>21</v>
+      <c r="G27" s="14">
+        <v>1</v>
+      </c>
+      <c r="H27" s="15">
+        <v>200</v>
       </c>
       <c r="I27" s="14">
+        <v>7</v>
+      </c>
+      <c r="J27" s="14">
         <v>5</v>
       </c>
-      <c r="J27" s="14">
-        <v>4</v>
-      </c>
       <c r="K27" s="15">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="L27" s="15">
-        <v>400</v>
+        <v>600</v>
       </c>
       <c r="M27" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1434,26 +1434,26 @@
       <c r="E28" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F28" s="13" t="s">
-        <v>20</v>
+      <c r="F28" s="14">
+        <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H28" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I28" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="J28" s="14">
         <v>15</v>
       </c>
       <c r="K28" s="15">
-        <v>-66.666666666666</v>
+        <v>-60</v>
       </c>
       <c r="L28" s="15">
-        <v>-50</v>
+        <v>-40</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1466,32 +1466,32 @@
       <c r="A29" s="13" t="s">
         <v>36</v>
       </c>
-      <c r="C29" s="14">
-        <v>1</v>
-      </c>
-      <c r="D29" s="13" t="s">
+      <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
+      <c r="D29" s="14">
+        <v>1</v>
+      </c>
+      <c r="E29" s="15">
+        <v>-100</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
       </c>
-      <c r="G29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H29" s="13" t="s">
-        <v>21</v>
+      <c r="G29" s="14">
+        <v>1</v>
+      </c>
+      <c r="H29" s="15">
+        <v>0</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K29" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,39 +1500,39 @@
         <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.551724137931</v>
+        <v>-96.875</v>
       </c>
     </row>
     <row r="30" spans="1:14">
       <c r="A30" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="C30" s="14">
-        <v>1</v>
-      </c>
-      <c r="D30" s="13" t="s">
+      <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
+      <c r="D30" s="14">
+        <v>1</v>
+      </c>
+      <c r="E30" s="15">
+        <v>-100</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
       </c>
-      <c r="G30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="H30" s="13" t="s">
-        <v>21</v>
+      <c r="G30" s="14">
+        <v>1</v>
+      </c>
+      <c r="H30" s="15">
+        <v>0</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="K30" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-95.833333333333</v>
+        <v>-96.296296296296</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1552,7 +1552,7 @@
         <v>20</v>
       </c>
       <c r="D31" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E31" s="15">
         <v>-100</v>
@@ -1561,7 +1561,7 @@
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">16</t>
+      <t xml:space="preserve">17</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/13/2026</t>
+      <t xml:space="preserve">4/20/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/19/2026</t>
+      <t xml:space="preserve">4/26/2026</t>
     </r>
   </si>
   <si>
@@ -892,23 +892,23 @@
       <c r="A15" s="13" t="s">
         <v>22</v>
       </c>
-      <c r="C15" s="14">
+      <c r="C15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D15" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E15" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F15" s="14">
         <v>2</v>
-      </c>
-      <c r="D15" s="14">
-        <v>1</v>
-      </c>
-      <c r="E15" s="15">
-        <v>100</v>
-      </c>
-      <c r="F15" s="14">
-        <v>3</v>
       </c>
       <c r="G15" s="14">
         <v>1</v>
       </c>
       <c r="H15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I15" s="14">
         <v>6</v>
@@ -923,51 +923,51 @@
         <v>500</v>
       </c>
       <c r="M15" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="N15" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="13" t="s">
-        <v>20</v>
+      <c r="C16" s="14">
+        <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E16" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G16" s="14">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="H16" s="15">
-        <v>-70</v>
+        <v>-63.636363636363</v>
       </c>
       <c r="I16" s="14">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="J16" s="14">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="K16" s="15">
-        <v>-44.117647058823</v>
+        <v>-40.540540540540</v>
       </c>
       <c r="L16" s="15">
-        <v>-29.629629629629</v>
+        <v>-24.137931034482</v>
       </c>
       <c r="M16" s="15">
-        <v>-68.333333333333</v>
+        <v>-65.079365079365</v>
       </c>
       <c r="N16" s="15">
-        <v>-94.080996884735</v>
+        <v>-93.510324483775</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,40 +975,40 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D17" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="E17" s="15">
-        <v>-83.333333333333</v>
+        <v>-71.428571428571</v>
       </c>
       <c r="F17" s="14">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G17" s="14">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="H17" s="15">
-        <v>-28.571428571428</v>
+        <v>-52.631578947368</v>
       </c>
       <c r="I17" s="14">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="J17" s="14">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="K17" s="15">
-        <v>-8.955223880597</v>
+        <v>-14.864864864864</v>
       </c>
       <c r="L17" s="15">
-        <v>24.489795918367</v>
+        <v>14.545454545454</v>
       </c>
       <c r="M17" s="15">
-        <v>90.625</v>
+        <v>85.294117647058</v>
       </c>
       <c r="N17" s="15">
-        <v>-54.135338345864</v>
+        <v>-53.676470588235</v>
       </c>
     </row>
     <row r="18" spans="1:14">
@@ -1016,40 +1016,40 @@
         <v>25</v>
       </c>
       <c r="C18" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D18" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E18" s="15">
-        <v>0</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F18" s="14">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="H18" s="15">
         <v>-33.333333333333</v>
       </c>
       <c r="I18" s="14">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="K18" s="15">
-        <v>-11.111111111111</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="L18" s="15">
+        <v>-48.571428571428</v>
+      </c>
+      <c r="M18" s="15">
         <v>-50</v>
       </c>
-      <c r="M18" s="15">
-        <v>-54.285714285714</v>
-      </c>
       <c r="N18" s="15">
-        <v>-92.488262910798</v>
+        <v>-92.070484581497</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,81 +1057,81 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D19" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E19" s="15">
-        <v>-50</v>
+        <v>-44.444444444444</v>
       </c>
       <c r="F19" s="14">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G19" s="14">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="H19" s="15">
-        <v>-37.5</v>
+        <v>-43.333333333333</v>
       </c>
       <c r="I19" s="14">
-        <v>72</v>
+        <v>77</v>
       </c>
       <c r="J19" s="14">
-        <v>99</v>
+        <v>108</v>
       </c>
       <c r="K19" s="15">
-        <v>-27.272727272727</v>
+        <v>-28.703703703703</v>
       </c>
       <c r="L19" s="15">
-        <v>2.857142857142</v>
+        <v>4.054054054054</v>
       </c>
       <c r="M19" s="15">
-        <v>-35.714285714285</v>
+        <v>-34.188034188034</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.571428571428</v>
+        <v>-48.666666666666</v>
       </c>
     </row>
     <row r="20" spans="1:14">
       <c r="A20" s="13" t="s">
         <v>27</v>
       </c>
-      <c r="C20" s="13" t="s">
-        <v>20</v>
+      <c r="C20" s="14">
+        <v>2</v>
       </c>
       <c r="D20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>-100</v>
+        <v>100</v>
       </c>
       <c r="F20" s="14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G20" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H20" s="15">
-        <v>-28.571428571428</v>
+        <v>-25</v>
       </c>
       <c r="I20" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="J20" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K20" s="15">
-        <v>0</v>
+        <v>4.166666666666</v>
       </c>
       <c r="L20" s="15">
-        <v>-50</v>
+        <v>-48.979591836734</v>
       </c>
       <c r="M20" s="15">
-        <v>0</v>
+        <v>-3.846153846153</v>
       </c>
       <c r="N20" s="15">
-        <v>-90.212765957446</v>
+        <v>-89.837398373983</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,78 +1139,78 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="E21" s="18">
-        <v>-60</v>
+        <v>-39.130434782608</v>
       </c>
       <c r="F21" s="17">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="G21" s="17">
-        <v>59</v>
+        <v>75</v>
       </c>
       <c r="H21" s="18">
-        <v>-33.898305084745</v>
+        <v>-42.666666666666</v>
       </c>
       <c r="I21" s="17">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="J21" s="17">
-        <v>248</v>
+        <v>271</v>
       </c>
       <c r="K21" s="18">
-        <v>-20.161290322580</v>
+        <v>-21.771217712177</v>
       </c>
       <c r="L21" s="18">
-        <v>-12.389380530973</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="M21" s="18">
-        <v>-25.563909774436</v>
+        <v>-24.555160142348</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.373471307619</v>
+        <v>-81.071428571428</v>
       </c>
     </row>
     <row r="22" spans="1:14">
       <c r="A22" s="13" t="s">
         <v>29</v>
       </c>
-      <c r="C22" s="13" t="s">
-        <v>20</v>
+      <c r="C22" s="14">
+        <v>1</v>
       </c>
       <c r="D22" s="14">
         <v>1</v>
       </c>
       <c r="E22" s="15">
-        <v>-100</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>20</v>
+        <v>0</v>
+      </c>
+      <c r="F22" s="14">
+        <v>1</v>
       </c>
       <c r="G22" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-100</v>
+        <v>-80</v>
       </c>
       <c r="I22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J22" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="K22" s="15">
         <v>0</v>
       </c>
       <c r="L22" s="15">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="M22" s="15">
-        <v>-60</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="13" t="s">
-        <v>20</v>
+      <c r="C23" s="14">
+        <v>1</v>
       </c>
       <c r="D23" s="14">
         <v>3</v>
       </c>
       <c r="E23" s="15">
-        <v>-100</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F23" s="14">
+        <v>5</v>
+      </c>
+      <c r="G23" s="14">
         <v>6</v>
       </c>
-      <c r="G23" s="14">
-        <v>4</v>
-      </c>
       <c r="H23" s="15">
+        <v>-16.666666666666</v>
+      </c>
+      <c r="I23" s="14">
+        <v>31</v>
+      </c>
+      <c r="J23" s="14">
         <v>50</v>
       </c>
-      <c r="I23" s="14">
-        <v>30</v>
-      </c>
-      <c r="J23" s="14">
-        <v>47</v>
-      </c>
       <c r="K23" s="15">
-        <v>-36.170212765957</v>
+        <v>-38</v>
       </c>
       <c r="L23" s="15">
-        <v>3.448275862068</v>
+        <v>-3.125</v>
       </c>
       <c r="M23" s="15">
-        <v>7.142857142857</v>
+        <v>3.333333333333</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="D24" s="14">
         <v>9</v>
       </c>
       <c r="E24" s="15">
-        <v>-44.444444444444</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F24" s="14">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="H24" s="15">
-        <v>-20.930232558139</v>
+        <v>-7.692307692307</v>
       </c>
       <c r="I24" s="14">
-        <v>145</v>
+        <v>155</v>
       </c>
       <c r="J24" s="14">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="K24" s="15">
-        <v>-17.613636363636</v>
+        <v>-16.216216216216</v>
       </c>
       <c r="L24" s="15">
-        <v>-11.585365853658</v>
+        <v>-15.300546448087</v>
       </c>
       <c r="M24" s="15">
-        <v>-44.015444015444</v>
+        <v>-45.035460992907</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E25" s="15">
-        <v>0</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F25" s="14">
+        <v>11</v>
+      </c>
+      <c r="G25" s="14">
         <v>10</v>
       </c>
-      <c r="G25" s="14">
-        <v>9</v>
-      </c>
       <c r="H25" s="15">
-        <v>11.111111111111</v>
+        <v>10</v>
       </c>
       <c r="I25" s="14">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="J25" s="14">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="K25" s="15">
-        <v>-14.893617021276</v>
+        <v>-12</v>
       </c>
       <c r="L25" s="15">
-        <v>-20</v>
+        <v>-21.428571428571</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D26" s="14">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="E26" s="15">
-        <v>37.5</v>
+        <v>11.111111111111</v>
       </c>
       <c r="F26" s="14">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.225806451612</v>
+        <v>-3.125</v>
       </c>
       <c r="I26" s="14">
-        <v>97</v>
+        <v>107</v>
       </c>
       <c r="J26" s="14">
-        <v>102</v>
+        <v>111</v>
       </c>
       <c r="K26" s="15">
-        <v>-4.901960784313</v>
+        <v>-3.603603603603</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.185185185185</v>
+        <v>-10.084033613445</v>
       </c>
       <c r="M26" s="15">
-        <v>16.867469879518</v>
+        <v>20.224719101123</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1384,23 +1384,23 @@
       <c r="A27" s="13" t="s">
         <v>34</v>
       </c>
-      <c r="C27" s="14">
+      <c r="C27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D27" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E27" s="13" t="s">
+        <v>21</v>
+      </c>
+      <c r="F27" s="14">
         <v>2</v>
-      </c>
-      <c r="D27" s="14">
-        <v>1</v>
-      </c>
-      <c r="E27" s="15">
-        <v>100</v>
-      </c>
-      <c r="F27" s="14">
-        <v>3</v>
       </c>
       <c r="G27" s="14">
         <v>1</v>
       </c>
       <c r="H27" s="15">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="I27" s="14">
         <v>7</v>
@@ -1425,14 +1425,14 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="14">
-        <v>1</v>
-      </c>
-      <c r="D28" s="13" t="s">
+      <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="E28" s="13" t="s">
-        <v>21</v>
+      <c r="D28" s="14">
+        <v>3</v>
+      </c>
+      <c r="E28" s="15">
+        <v>-100</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
@@ -1447,10 +1447,10 @@
         <v>6</v>
       </c>
       <c r="J28" s="14">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-60</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="L28" s="15">
         <v>-40</v>
@@ -1469,11 +1469,11 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="14">
-        <v>1</v>
-      </c>
-      <c r="E29" s="15">
-        <v>-100</v>
+      <c r="D29" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E29" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F29" s="14">
         <v>1</v>
@@ -1510,11 +1510,11 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="14">
-        <v>1</v>
-      </c>
-      <c r="E30" s="15">
-        <v>-100</v>
+      <c r="D30" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E30" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F30" s="14">
         <v>1</v>
@@ -1551,11 +1551,11 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="14">
-        <v>1</v>
-      </c>
-      <c r="E31" s="15">
-        <v>-100</v>
+      <c r="D31" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E31" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">17</t>
+      <t xml:space="preserve">18</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/20/2026</t>
+      <t xml:space="preserve">4/27/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/26/2026</t>
+      <t xml:space="preserve">5/3/2026</t>
     </r>
   </si>
   <si>
@@ -937,37 +937,37 @@
         <v>3</v>
       </c>
       <c r="D16" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="E16" s="15">
-        <v>0</v>
+        <v>-25</v>
       </c>
       <c r="F16" s="14">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G16" s="14">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="H16" s="15">
-        <v>-63.636363636363</v>
+        <v>-53.333333333333</v>
       </c>
       <c r="I16" s="14">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="J16" s="14">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>-40.540540540540</v>
+        <v>-39.024390243902</v>
       </c>
       <c r="L16" s="15">
-        <v>-24.137931034482</v>
+        <v>-19.354838709677</v>
       </c>
       <c r="M16" s="15">
-        <v>-65.079365079365</v>
+        <v>-60.9375</v>
       </c>
       <c r="N16" s="15">
-        <v>-93.510324483775</v>
+        <v>-92.937853107344</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -975,81 +975,81 @@
         <v>24</v>
       </c>
       <c r="C17" s="14">
+        <v>4</v>
+      </c>
+      <c r="D17" s="14">
         <v>2</v>
       </c>
-      <c r="D17" s="14">
-        <v>7</v>
-      </c>
       <c r="E17" s="15">
-        <v>-71.428571428571</v>
+        <v>100</v>
       </c>
       <c r="F17" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G17" s="14">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="15">
-        <v>-52.631578947368</v>
+        <v>-38.888888888888</v>
       </c>
       <c r="I17" s="14">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="J17" s="14">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="K17" s="15">
-        <v>-14.864864864864</v>
+        <v>-11.842105263157</v>
       </c>
       <c r="L17" s="15">
-        <v>14.545454545454</v>
+        <v>13.559322033898</v>
       </c>
       <c r="M17" s="15">
-        <v>85.294117647058</v>
+        <v>81.081081081081</v>
       </c>
       <c r="N17" s="15">
-        <v>-53.676470588235</v>
+        <v>-53.793103448275</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" s="14">
         <v>2</v>
       </c>
-      <c r="D18" s="14">
+      <c r="E18" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F18" s="14">
         <v>3</v>
       </c>
-      <c r="E18" s="15">
-        <v>-33.333333333333</v>
-      </c>
-      <c r="F18" s="14">
-        <v>4</v>
-      </c>
       <c r="G18" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-33.333333333333</v>
+        <v>-57.142857142857</v>
       </c>
       <c r="I18" s="14">
         <v>18</v>
       </c>
       <c r="J18" s="14">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="K18" s="15">
-        <v>-14.285714285714</v>
+        <v>-21.739130434782</v>
       </c>
       <c r="L18" s="15">
-        <v>-48.571428571428</v>
+        <v>-51.351351351351</v>
       </c>
       <c r="M18" s="15">
-        <v>-50</v>
+        <v>-53.846153846153</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.070484581497</v>
+        <v>-92.653061224489</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1057,40 +1057,40 @@
         <v>26</v>
       </c>
       <c r="C19" s="14">
+        <v>8</v>
+      </c>
+      <c r="D19" s="14">
         <v>5</v>
       </c>
-      <c r="D19" s="14">
-        <v>9</v>
-      </c>
       <c r="E19" s="15">
-        <v>-44.444444444444</v>
+        <v>60</v>
       </c>
       <c r="F19" s="14">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="G19" s="14">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="H19" s="15">
-        <v>-43.333333333333</v>
+        <v>-14.814814814814</v>
       </c>
       <c r="I19" s="14">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="J19" s="14">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="K19" s="15">
-        <v>-28.703703703703</v>
+        <v>-24.778761061946</v>
       </c>
       <c r="L19" s="15">
-        <v>4.054054054054</v>
+        <v>10.389610389610</v>
       </c>
       <c r="M19" s="15">
-        <v>-34.188034188034</v>
+        <v>-30.894308943089</v>
       </c>
       <c r="N19" s="15">
-        <v>-48.666666666666</v>
+        <v>-49.404761904761</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1098,40 +1098,40 @@
         <v>27</v>
       </c>
       <c r="C20" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D20" s="14">
         <v>1</v>
       </c>
       <c r="E20" s="15">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="F20" s="14">
+        <v>4</v>
+      </c>
+      <c r="G20" s="14">
         <v>6</v>
       </c>
-      <c r="G20" s="14">
-        <v>8</v>
-      </c>
       <c r="H20" s="15">
-        <v>-25</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I20" s="14">
+        <v>26</v>
+      </c>
+      <c r="J20" s="14">
         <v>25</v>
       </c>
-      <c r="J20" s="14">
-        <v>24</v>
-      </c>
       <c r="K20" s="15">
-        <v>4.166666666666</v>
+        <v>4</v>
       </c>
       <c r="L20" s="15">
-        <v>-48.979591836734</v>
+        <v>-46.938775510204</v>
       </c>
       <c r="M20" s="15">
-        <v>-3.846153846153</v>
+        <v>-13.333333333333</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.837398373983</v>
+        <v>-89.883268482490</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
+        <v>16</v>
+      </c>
+      <c r="D21" s="17">
         <v>14</v>
       </c>
-      <c r="D21" s="17">
-        <v>23</v>
-      </c>
       <c r="E21" s="18">
-        <v>-39.130434782608</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F21" s="17">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="G21" s="17">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="H21" s="18">
-        <v>-42.666666666666</v>
+        <v>-31.081081081081</v>
       </c>
       <c r="I21" s="17">
-        <v>212</v>
+        <v>228</v>
       </c>
       <c r="J21" s="17">
-        <v>271</v>
+        <v>285</v>
       </c>
       <c r="K21" s="18">
-        <v>-21.771217712177</v>
+        <v>-20</v>
       </c>
       <c r="L21" s="18">
-        <v>-13.114754098360</v>
+        <v>-10.588235294117</v>
       </c>
       <c r="M21" s="18">
-        <v>-24.555160142348</v>
+        <v>-23.489932885906</v>
       </c>
       <c r="N21" s="18">
-        <v>-81.071428571428</v>
+        <v>-80.856423173803</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1182,35 +1182,35 @@
       <c r="C22" s="14">
         <v>1</v>
       </c>
-      <c r="D22" s="14">
-        <v>1</v>
-      </c>
-      <c r="E22" s="15">
-        <v>0</v>
+      <c r="D22" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F22" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G22" s="14">
         <v>5</v>
       </c>
       <c r="H22" s="15">
-        <v>-80</v>
+        <v>-60</v>
       </c>
       <c r="I22" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>0</v>
+        <v>14.285714285714</v>
       </c>
       <c r="L22" s="15">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-53.333333333333</v>
+        <v>-46.666666666666</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1221,37 +1221,37 @@
         <v>30</v>
       </c>
       <c r="C23" s="14">
+        <v>4</v>
+      </c>
+      <c r="D23" s="14">
         <v>1</v>
       </c>
-      <c r="D23" s="14">
-        <v>3</v>
-      </c>
       <c r="E23" s="15">
-        <v>-66.666666666666</v>
+        <v>300</v>
       </c>
       <c r="F23" s="14">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G23" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H23" s="15">
-        <v>-16.666666666666</v>
+        <v>14.285714285714</v>
       </c>
       <c r="I23" s="14">
-        <v>31</v>
+        <v>35</v>
       </c>
       <c r="J23" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K23" s="15">
-        <v>-38</v>
+        <v>-31.372549019607</v>
       </c>
       <c r="L23" s="15">
-        <v>-3.125</v>
+        <v>9.375</v>
       </c>
       <c r="M23" s="15">
-        <v>3.333333333333</v>
+        <v>9.375</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D24" s="14">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E24" s="15">
-        <v>11.111111111111</v>
+        <v>33.333333333333</v>
       </c>
       <c r="F24" s="14">
-        <v>36</v>
+        <v>30</v>
       </c>
       <c r="G24" s="14">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H24" s="15">
-        <v>-7.692307692307</v>
+        <v>-26.829268292682</v>
       </c>
       <c r="I24" s="14">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="J24" s="14">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="K24" s="15">
-        <v>-16.216216216216</v>
+        <v>-14.659685863874</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.300546448087</v>
+        <v>-15.979381443299</v>
       </c>
       <c r="M24" s="15">
-        <v>-45.035460992907</v>
+        <v>-46.905537459283</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1306,31 +1306,31 @@
         <v>4</v>
       </c>
       <c r="D25" s="14">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="E25" s="15">
-        <v>33.333333333333</v>
+        <v>300</v>
       </c>
       <c r="F25" s="14">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G25" s="14">
         <v>10</v>
       </c>
       <c r="H25" s="15">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I25" s="14">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="J25" s="14">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="K25" s="15">
-        <v>-12</v>
+        <v>-5.882352941176</v>
       </c>
       <c r="L25" s="15">
-        <v>-21.428571428571</v>
+        <v>-20</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="14">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="E26" s="15">
-        <v>11.111111111111</v>
+        <v>-45.454545454545</v>
       </c>
       <c r="F26" s="14">
         <v>31</v>
       </c>
       <c r="G26" s="14">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="H26" s="15">
-        <v>-3.125</v>
+        <v>3.333333333333</v>
       </c>
       <c r="I26" s="14">
-        <v>107</v>
+        <v>112</v>
       </c>
       <c r="J26" s="14">
-        <v>111</v>
+        <v>122</v>
       </c>
       <c r="K26" s="15">
-        <v>-3.603603603603</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="L26" s="15">
-        <v>-10.084033613445</v>
+        <v>-8.196721311475</v>
       </c>
       <c r="M26" s="15">
-        <v>20.224719101123</v>
+        <v>16.666666666666</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1428,20 +1428,20 @@
       <c r="C28" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D28" s="14">
-        <v>3</v>
-      </c>
-      <c r="E28" s="15">
-        <v>-100</v>
+      <c r="D28" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E28" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F28" s="14">
         <v>1</v>
       </c>
       <c r="G28" s="14">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-80</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="I28" s="14">
         <v>6</v>
@@ -1500,7 +1500,7 @@
         <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.875</v>
+        <v>-96.969696969697</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1541,7 +1541,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.296296296296</v>
+        <v>-96.428571428571</v>
       </c>
     </row>
     <row r="31" spans="1:14">

--- a/data/source/weekly/cs-en-us-088pct.xlsx
+++ b/data/source/weekly/cs-en-us-088pct.xlsx
@@ -69,7 +69,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">18</t>
+      <t xml:space="preserve">19</t>
     </r>
   </si>
   <si>
@@ -95,7 +95,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">4/27/2026</t>
+      <t xml:space="preserve">5/4/2026</t>
     </r>
     <r>
       <rPr>
@@ -113,7 +113,7 @@
         <family val="2"/>
         <rFont val="Andale WT"/>
       </rPr>
-      <t xml:space="preserve">5/3/2026</t>
+      <t xml:space="preserve">5/10/2026</t>
     </r>
   </si>
   <si>
@@ -860,8 +860,8 @@
       <c r="E14" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="F14" s="14">
-        <v>1</v>
+      <c r="F14" s="13" t="s">
+        <v>20</v>
       </c>
       <c r="G14" s="13" t="s">
         <v>20</v>
@@ -882,10 +882,10 @@
         <v>0</v>
       </c>
       <c r="M14" s="15">
-        <v>-50</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="N14" s="15">
-        <v>-88.888888888888</v>
+        <v>-90.909090909090</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -933,41 +933,41 @@
       <c r="A16" s="13" t="s">
         <v>23</v>
       </c>
-      <c r="C16" s="14">
-        <v>3</v>
-      </c>
-      <c r="D16" s="14">
-        <v>4</v>
-      </c>
-      <c r="E16" s="15">
-        <v>-25</v>
+      <c r="C16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D16" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="E16" s="13" t="s">
+        <v>21</v>
       </c>
       <c r="F16" s="14">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G16" s="14">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H16" s="15">
-        <v>-53.333333333333</v>
+        <v>-11.111111111111</v>
       </c>
       <c r="I16" s="14">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" s="14">
         <v>41</v>
       </c>
       <c r="K16" s="15">
-        <v>-39.024390243902</v>
+        <v>-34.146341463414</v>
       </c>
       <c r="L16" s="15">
-        <v>-19.354838709677</v>
+        <v>-15.625</v>
       </c>
       <c r="M16" s="15">
-        <v>-60.9375</v>
+        <v>-58.461538461538</v>
       </c>
       <c r="N16" s="15">
-        <v>-92.937853107344</v>
+        <v>-92.741935483871</v>
       </c>
     </row>
     <row r="17" spans="1:14">
@@ -978,78 +978,78 @@
         <v>4</v>
       </c>
       <c r="D17" s="14">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="E17" s="15">
-        <v>100</v>
+        <v>-60</v>
       </c>
       <c r="F17" s="14">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G17" s="14">
-        <v>18</v>
+        <v>25</v>
       </c>
       <c r="H17" s="15">
-        <v>-38.888888888888</v>
+        <v>-52</v>
       </c>
       <c r="I17" s="14">
-        <v>67</v>
+        <v>72</v>
       </c>
       <c r="J17" s="14">
-        <v>76</v>
+        <v>86</v>
       </c>
       <c r="K17" s="15">
-        <v>-11.842105263157</v>
+        <v>-16.279069767441</v>
       </c>
       <c r="L17" s="15">
-        <v>13.559322033898</v>
+        <v>16.129032258064</v>
       </c>
       <c r="M17" s="15">
-        <v>81.081081081081</v>
+        <v>84.615384615384</v>
       </c>
       <c r="N17" s="15">
-        <v>-53.793103448275</v>
+        <v>-54.716981132075</v>
       </c>
     </row>
     <row r="18" spans="1:14">
       <c r="A18" s="13" t="s">
         <v>25</v>
       </c>
-      <c r="C18" s="13" t="s">
-        <v>20</v>
+      <c r="C18" s="14">
+        <v>1</v>
       </c>
       <c r="D18" s="14">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E18" s="15">
-        <v>-100</v>
+        <v>0</v>
       </c>
       <c r="F18" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G18" s="14">
         <v>7</v>
       </c>
       <c r="H18" s="15">
-        <v>-57.142857142857</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I18" s="14">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J18" s="14">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="K18" s="15">
-        <v>-21.739130434782</v>
+        <v>-20.833333333333</v>
       </c>
       <c r="L18" s="15">
-        <v>-51.351351351351</v>
+        <v>-51.282051282051</v>
       </c>
       <c r="M18" s="15">
-        <v>-53.846153846153</v>
+        <v>-54.761904761904</v>
       </c>
       <c r="N18" s="15">
-        <v>-92.653061224489</v>
+        <v>-92.775665399239</v>
       </c>
     </row>
     <row r="19" spans="1:14">
@@ -1060,37 +1060,37 @@
         <v>8</v>
       </c>
       <c r="D19" s="14">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E19" s="15">
-        <v>60</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F19" s="14">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="G19" s="14">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="H19" s="15">
-        <v>-14.814814814814</v>
+        <v>-13.793103448275</v>
       </c>
       <c r="I19" s="14">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="J19" s="14">
-        <v>113</v>
+        <v>120</v>
       </c>
       <c r="K19" s="15">
-        <v>-24.778761061946</v>
+        <v>-22.5</v>
       </c>
       <c r="L19" s="15">
-        <v>10.389610389610</v>
+        <v>10.714285714285</v>
       </c>
       <c r="M19" s="15">
-        <v>-30.894308943089</v>
+        <v>-29.007633587786</v>
       </c>
       <c r="N19" s="15">
-        <v>-49.404761904761</v>
+        <v>-46.551724137931</v>
       </c>
     </row>
     <row r="20" spans="1:14">
@@ -1101,37 +1101,37 @@
         <v>1</v>
       </c>
       <c r="D20" s="14">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E20" s="15">
-        <v>0</v>
+        <v>-66.666666666666</v>
       </c>
       <c r="F20" s="14">
         <v>4</v>
       </c>
       <c r="G20" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H20" s="15">
-        <v>-33.333333333333</v>
+        <v>-42.857142857142</v>
       </c>
       <c r="I20" s="14">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="J20" s="14">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="K20" s="15">
-        <v>4</v>
+        <v>-3.571428571428</v>
       </c>
       <c r="L20" s="15">
-        <v>-46.938775510204</v>
+        <v>-49.056603773584</v>
       </c>
       <c r="M20" s="15">
-        <v>-13.333333333333</v>
+        <v>-15.625</v>
       </c>
       <c r="N20" s="15">
-        <v>-89.883268482490</v>
+        <v>-90.109890109890</v>
       </c>
     </row>
     <row r="21" spans="1:14">
@@ -1139,40 +1139,40 @@
         <v>28</v>
       </c>
       <c r="C21" s="17">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="D21" s="17">
-        <v>14</v>
+        <v>21</v>
       </c>
       <c r="E21" s="18">
-        <v>14.285714285714</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="F21" s="17">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G21" s="17">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="H21" s="18">
-        <v>-31.081081081081</v>
+        <v>-29.487179487179</v>
       </c>
       <c r="I21" s="17">
-        <v>228</v>
+        <v>245</v>
       </c>
       <c r="J21" s="17">
-        <v>285</v>
+        <v>306</v>
       </c>
       <c r="K21" s="18">
-        <v>-20</v>
+        <v>-19.934640522875</v>
       </c>
       <c r="L21" s="18">
-        <v>-10.588235294117</v>
+        <v>-9.926470588235</v>
       </c>
       <c r="M21" s="18">
-        <v>-23.489932885906</v>
+        <v>-22.222222222222</v>
       </c>
       <c r="N21" s="18">
-        <v>-80.856423173803</v>
+        <v>-80.632411067193</v>
       </c>
     </row>
     <row r="22" spans="1:14">
@@ -1189,28 +1189,28 @@
         <v>21</v>
       </c>
       <c r="F22" s="14">
+        <v>4</v>
+      </c>
+      <c r="G22" s="14">
         <v>2</v>
       </c>
-      <c r="G22" s="14">
-        <v>5</v>
-      </c>
       <c r="H22" s="15">
-        <v>-60</v>
+        <v>100</v>
       </c>
       <c r="I22" s="14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J22" s="14">
         <v>7</v>
       </c>
       <c r="K22" s="15">
-        <v>14.285714285714</v>
+        <v>42.857142857142</v>
       </c>
       <c r="L22" s="15">
         <v>100</v>
       </c>
       <c r="M22" s="15">
-        <v>-46.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="N22" s="13" t="s">
         <v>21</v>
@@ -1220,38 +1220,38 @@
       <c r="A23" s="13" t="s">
         <v>30</v>
       </c>
-      <c r="C23" s="14">
+      <c r="C23" s="13" t="s">
+        <v>20</v>
+      </c>
+      <c r="D23" s="14">
         <v>4</v>
       </c>
-      <c r="D23" s="14">
-        <v>1</v>
-      </c>
       <c r="E23" s="15">
-        <v>300</v>
+        <v>-100</v>
       </c>
       <c r="F23" s="14">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G23" s="14">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="H23" s="15">
-        <v>14.285714285714</v>
+        <v>-36.363636363636</v>
       </c>
       <c r="I23" s="14">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="J23" s="14">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="K23" s="15">
-        <v>-31.372549019607</v>
+        <v>-32.727272727272</v>
       </c>
       <c r="L23" s="15">
-        <v>9.375</v>
+        <v>8.823529411764</v>
       </c>
       <c r="M23" s="15">
-        <v>9.375</v>
+        <v>8.823529411764</v>
       </c>
       <c r="N23" s="13" t="s">
         <v>21</v>
@@ -1262,37 +1262,37 @@
         <v>31</v>
       </c>
       <c r="C24" s="14">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="D24" s="14">
-        <v>6</v>
+        <v>18</v>
       </c>
       <c r="E24" s="15">
-        <v>33.333333333333</v>
+        <v>-27.777777777777</v>
       </c>
       <c r="F24" s="14">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="G24" s="14">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="H24" s="15">
-        <v>-26.829268292682</v>
+        <v>-14.285714285714</v>
       </c>
       <c r="I24" s="14">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="J24" s="14">
-        <v>191</v>
+        <v>209</v>
       </c>
       <c r="K24" s="15">
-        <v>-14.659685863874</v>
+        <v>-15.789473684210</v>
       </c>
       <c r="L24" s="15">
-        <v>-15.979381443299</v>
+        <v>-14.563106796116</v>
       </c>
       <c r="M24" s="15">
-        <v>-46.905537459283</v>
+        <v>-47.462686567164</v>
       </c>
       <c r="N24" s="13" t="s">
         <v>21</v>
@@ -1303,34 +1303,34 @@
         <v>32</v>
       </c>
       <c r="C25" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D25" s="14">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="E25" s="15">
-        <v>300</v>
+        <v>-28.571428571428</v>
       </c>
       <c r="F25" s="14">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="G25" s="14">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H25" s="15">
-        <v>0</v>
+        <v>16.666666666666</v>
       </c>
       <c r="I25" s="14">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="J25" s="14">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="K25" s="15">
-        <v>-5.882352941176</v>
+        <v>-8.620689655172</v>
       </c>
       <c r="L25" s="15">
-        <v>-20</v>
+        <v>-13.114754098360</v>
       </c>
       <c r="M25" s="13" t="s">
         <v>21</v>
@@ -1344,37 +1344,37 @@
         <v>33</v>
       </c>
       <c r="C26" s="14">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="D26" s="14">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E26" s="15">
-        <v>-45.454545454545</v>
+        <v>14.285714285714</v>
       </c>
       <c r="F26" s="14">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G26" s="14">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H26" s="15">
-        <v>3.333333333333</v>
+        <v>-8.571428571428</v>
       </c>
       <c r="I26" s="14">
-        <v>112</v>
+        <v>118</v>
       </c>
       <c r="J26" s="14">
-        <v>122</v>
+        <v>129</v>
       </c>
       <c r="K26" s="15">
-        <v>-8.196721311475</v>
+        <v>-8.527131782945</v>
       </c>
       <c r="L26" s="15">
-        <v>-8.196721311475</v>
+        <v>-9.230769230769</v>
       </c>
       <c r="M26" s="15">
-        <v>16.666666666666</v>
+        <v>14.563106796116</v>
       </c>
       <c r="N26" s="13" t="s">
         <v>21</v>
@@ -1425,8 +1425,8 @@
       <c r="A28" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="C28" s="13" t="s">
-        <v>20</v>
+      <c r="C28" s="14">
+        <v>1</v>
       </c>
       <c r="D28" s="13" t="s">
         <v>20</v>
@@ -1435,25 +1435,25 @@
         <v>21</v>
       </c>
       <c r="F28" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G28" s="14">
         <v>3</v>
       </c>
       <c r="H28" s="15">
-        <v>-66.666666666666</v>
+        <v>-33.333333333333</v>
       </c>
       <c r="I28" s="14">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="J28" s="14">
         <v>18</v>
       </c>
       <c r="K28" s="15">
-        <v>-66.666666666666</v>
+        <v>-61.111111111111</v>
       </c>
       <c r="L28" s="15">
-        <v>-40</v>
+        <v>-30</v>
       </c>
       <c r="M28" s="13" t="s">
         <v>21</v>
@@ -1469,29 +1469,29 @@
       <c r="C29" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D29" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F29" s="14">
+      <c r="D29" s="14">
         <v>1</v>
       </c>
+      <c r="E29" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F29" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G29" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H29" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I29" s="14">
         <v>1</v>
       </c>
       <c r="J29" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K29" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L29" s="13" t="s">
         <v>21</v>
@@ -1500,7 +1500,7 @@
         <v>-85.714285714285</v>
       </c>
       <c r="N29" s="15">
-        <v>-96.969696969697</v>
+        <v>-97.560975609756</v>
       </c>
     </row>
     <row r="30" spans="1:14">
@@ -1510,29 +1510,29 @@
       <c r="C30" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D30" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="13" t="s">
-        <v>21</v>
-      </c>
-      <c r="F30" s="14">
+      <c r="D30" s="14">
         <v>1</v>
       </c>
+      <c r="E30" s="15">
+        <v>-100</v>
+      </c>
+      <c r="F30" s="13" t="s">
+        <v>20</v>
+      </c>
       <c r="G30" s="14">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H30" s="15">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="I30" s="14">
         <v>1</v>
       </c>
       <c r="J30" s="14">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K30" s="15">
-        <v>-66.666666666666</v>
+        <v>-75</v>
       </c>
       <c r="L30" s="13" t="s">
         <v>21</v>
@@ -1541,7 +1541,7 @@
         <v>-83.333333333333</v>
       </c>
       <c r="N30" s="15">
-        <v>-96.428571428571</v>
+        <v>-97.058823529411</v>
       </c>
     </row>
     <row r="31" spans="1:14">
@@ -1551,17 +1551,17 @@
       <c r="C31" s="13" t="s">
         <v>20</v>
       </c>
-      <c r="D31" s="13" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="13" t="s">
-        <v>21</v>
+      <c r="D31" s="14">
+        <v>1</v>
+      </c>
+      <c r="E31" s="15">
+        <v>-100</v>
       </c>
       <c r="F31" s="13" t="s">
         <v>20</v>
       </c>
       <c r="G31" s="14">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H31" s="15">
         <v>-100</v>
@@ -1570,7 +1570,7 @@
         <v>20</v>
       </c>
       <c r="J31" s="14">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="K31" s="15">
         <v>-100</v>
